--- a/DATA/DATA FILES/VFD DATA.xlsx
+++ b/DATA/DATA FILES/VFD DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HHpro\DATA\DATA FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA873AF8-038F-4E99-B9F4-A2086DC95BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB40DAB6-F3F9-4ED8-B930-5E86BEB569DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{CF7C304B-F6B4-4B1F-B338-76877CE5AAA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CF7C304B-F6B4-4B1F-B338-76877CE5AAA5}"/>
   </bookViews>
   <sheets>
     <sheet name="SCHEDULE" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2168" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="249">
   <si>
     <t>VFD Schedule</t>
   </si>
@@ -781,6 +781,12 @@
   </si>
   <si>
     <t>OPERATION MANUAL</t>
+  </si>
+  <si>
+    <t>BYPASS</t>
+  </si>
+  <si>
+    <t>YES</t>
   </si>
 </sst>
 </file>
@@ -826,7 +832,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1146,11 +1152,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1191,12 +1236,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1206,13 +1245,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1244,6 +1280,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1579,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E601348-E0B6-45CC-BD60-AA1E3D8AABBC}">
-  <dimension ref="A1:AK180"/>
+  <dimension ref="A1:AL180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
@@ -1593,215 +1650,221 @@
     <col min="13" max="13" width="40" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="32" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="20" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="37" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="32" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="24"/>
-      <c r="O1" s="22" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="22"/>
+      <c r="O1" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="24"/>
-      <c r="T1" s="25" t="s">
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="22"/>
+      <c r="U1" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="27"/>
-    </row>
-    <row r="2" spans="1:37" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="28" t="s">
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="37"/>
+    </row>
+    <row r="2" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="30"/>
-      <c r="O2" s="20" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="27"/>
+      <c r="O2" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="S2" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="U2" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="V2" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="W2" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="W2" s="20" t="s">
+      <c r="X2" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="Y2" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="Z2" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AA2" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="AA2" s="20" t="s">
+      <c r="AB2" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="AB2" s="20" t="s">
+      <c r="AC2" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="AC2" s="20" t="s">
+      <c r="AD2" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="AD2" s="20" t="s">
+      <c r="AE2" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="AE2" s="20" t="s">
+      <c r="AF2" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="AF2" s="20" t="s">
+      <c r="AG2" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="AG2" s="20" t="s">
+      <c r="AH2" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="AH2" s="20" t="s">
+      <c r="AI2" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="AI2" s="20" t="s">
+      <c r="AJ2" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="AJ2" s="20" t="s">
+      <c r="AK2" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="AK2" s="20" t="s">
+      <c r="AL2" s="23" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="31" t="s">
+    <row r="3" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="31" t="s">
+      <c r="D3" s="31"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="31" t="s">
+      <c r="M3" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="21"/>
-      <c r="AI3" s="21"/>
-      <c r="AJ3" s="21"/>
-      <c r="AK3" s="21"/>
-    </row>
-    <row r="4" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
+      <c r="AJ3" s="24"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="24"/>
+    </row>
+    <row r="4" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
       <c r="C4" s="11" t="s">
         <v>12</v>
       </c>
@@ -1811,38 +1874,39 @@
       <c r="E4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="21"/>
-      <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="21"/>
-      <c r="AF4" s="21"/>
-      <c r="AG4" s="21"/>
-      <c r="AH4" s="21"/>
-      <c r="AI4" s="21"/>
-      <c r="AJ4" s="21"/>
-      <c r="AK4" s="21"/>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="24"/>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4">
@@ -1887,11 +1951,13 @@
       <c r="Q5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="T5" s="17"/>
-      <c r="U5" s="18"/>
+      <c r="R5" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="U5" s="17"/>
       <c r="V5" s="18"/>
       <c r="W5" s="18"/>
       <c r="X5" s="18"/>
@@ -1907,9 +1973,10 @@
       <c r="AH5" s="18"/>
       <c r="AI5" s="18"/>
       <c r="AJ5" s="18"/>
-      <c r="AK5" s="19"/>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK5" s="18"/>
+      <c r="AL5" s="19"/>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1954,11 +2021,13 @@
       <c r="Q6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="1"/>
+      <c r="R6" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U6" s="12"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
@@ -1974,9 +2043,10 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="13"/>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="13"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
@@ -2021,11 +2091,13 @@
       <c r="Q7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T7" s="12"/>
-      <c r="U7" s="1"/>
+      <c r="R7" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U7" s="12"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
@@ -2041,9 +2113,10 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
-      <c r="AK7" s="13"/>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="13"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -2088,11 +2161,13 @@
       <c r="Q8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T8" s="12"/>
-      <c r="U8" s="1"/>
+      <c r="R8" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U8" s="12"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
@@ -2108,9 +2183,10 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
-      <c r="AK8" s="13"/>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="13"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -2155,11 +2231,13 @@
       <c r="Q9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T9" s="12"/>
-      <c r="U9" s="1"/>
+      <c r="R9" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U9" s="12"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
@@ -2175,9 +2253,10 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="13"/>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="13"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -2222,11 +2301,13 @@
       <c r="Q10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T10" s="12"/>
-      <c r="U10" s="1"/>
+      <c r="R10" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U10" s="12"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
@@ -2242,9 +2323,10 @@
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
-      <c r="AK10" s="13"/>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="13"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -2289,11 +2371,13 @@
       <c r="Q11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T11" s="12"/>
-      <c r="U11" s="1"/>
+      <c r="R11" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U11" s="12"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
@@ -2309,9 +2393,10 @@
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
-      <c r="AK11" s="13"/>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK11" s="1"/>
+      <c r="AL11" s="13"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -2356,11 +2441,13 @@
       <c r="Q12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T12" s="12"/>
-      <c r="U12" s="1"/>
+      <c r="R12" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U12" s="12"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
@@ -2376,9 +2463,10 @@
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
-      <c r="AK12" s="13"/>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="13"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -2423,11 +2511,13 @@
       <c r="Q13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T13" s="12"/>
-      <c r="U13" s="1"/>
+      <c r="R13" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U13" s="12"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
@@ -2443,9 +2533,10 @@
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
-      <c r="AK13" s="13"/>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="13"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2">
@@ -2490,11 +2581,13 @@
       <c r="Q14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T14" s="12"/>
-      <c r="U14" s="1"/>
+      <c r="R14" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U14" s="12"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
@@ -2510,9 +2603,10 @@
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
-      <c r="AK14" s="13"/>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="13"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2">
@@ -2557,11 +2651,13 @@
       <c r="Q15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T15" s="12"/>
-      <c r="U15" s="1"/>
+      <c r="R15" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U15" s="12"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
@@ -2577,9 +2673,10 @@
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
-      <c r="AK15" s="13"/>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="13"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2">
@@ -2624,11 +2721,13 @@
       <c r="Q16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T16" s="12"/>
-      <c r="U16" s="1"/>
+      <c r="R16" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U16" s="12"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
@@ -2644,9 +2743,10 @@
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
-      <c r="AK16" s="13"/>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="13"/>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2">
@@ -2691,11 +2791,13 @@
       <c r="Q17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T17" s="12"/>
-      <c r="U17" s="1"/>
+      <c r="R17" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U17" s="12"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -2711,9 +2813,10 @@
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
-      <c r="AK17" s="13"/>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="13"/>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2">
@@ -2758,11 +2861,13 @@
       <c r="Q18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T18" s="12"/>
-      <c r="U18" s="1"/>
+      <c r="R18" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U18" s="12"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
@@ -2778,9 +2883,10 @@
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
-      <c r="AK18" s="13"/>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="13"/>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2">
@@ -2825,11 +2931,13 @@
       <c r="Q19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T19" s="12"/>
-      <c r="U19" s="1"/>
+      <c r="R19" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U19" s="12"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
@@ -2845,9 +2953,10 @@
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
-      <c r="AK19" s="13"/>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="13"/>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2">
@@ -2892,11 +3001,13 @@
       <c r="Q20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T20" s="12"/>
-      <c r="U20" s="1"/>
+      <c r="R20" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U20" s="12"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
@@ -2912,9 +3023,10 @@
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
-      <c r="AK20" s="13"/>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="13"/>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2">
@@ -2959,11 +3071,13 @@
       <c r="Q21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T21" s="12"/>
-      <c r="U21" s="1"/>
+      <c r="R21" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U21" s="12"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
@@ -2979,9 +3093,10 @@
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
-      <c r="AK21" s="13"/>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="13"/>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2">
@@ -3026,11 +3141,13 @@
       <c r="Q22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T22" s="12"/>
-      <c r="U22" s="1"/>
+      <c r="R22" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U22" s="12"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
@@ -3046,9 +3163,10 @@
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
-      <c r="AK22" s="13"/>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK22" s="1"/>
+      <c r="AL22" s="13"/>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2">
@@ -3093,11 +3211,13 @@
       <c r="Q23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R23" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T23" s="12"/>
-      <c r="U23" s="1"/>
+      <c r="R23" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U23" s="12"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
@@ -3113,9 +3233,10 @@
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
-      <c r="AK23" s="13"/>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK23" s="1"/>
+      <c r="AL23" s="13"/>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2">
@@ -3160,11 +3281,13 @@
       <c r="Q24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T24" s="12"/>
-      <c r="U24" s="1"/>
+      <c r="R24" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U24" s="12"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
@@ -3180,9 +3303,10 @@
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
-      <c r="AK24" s="13"/>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="13"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2">
@@ -3227,11 +3351,13 @@
       <c r="Q25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T25" s="12"/>
-      <c r="U25" s="1"/>
+      <c r="R25" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U25" s="12"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
@@ -3247,9 +3373,10 @@
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
-      <c r="AK25" s="13"/>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK25" s="1"/>
+      <c r="AL25" s="13"/>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2">
@@ -3294,11 +3421,13 @@
       <c r="Q26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T26" s="12"/>
-      <c r="U26" s="1"/>
+      <c r="R26" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U26" s="12"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
@@ -3314,9 +3443,10 @@
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
-      <c r="AK26" s="13"/>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="13"/>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2">
@@ -3361,11 +3491,13 @@
       <c r="Q27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T27" s="12"/>
-      <c r="U27" s="1"/>
+      <c r="R27" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U27" s="12"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
@@ -3381,9 +3513,10 @@
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
-      <c r="AK27" s="13"/>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="13"/>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2">
@@ -3428,11 +3561,13 @@
       <c r="Q28" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T28" s="12"/>
-      <c r="U28" s="1"/>
+      <c r="R28" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U28" s="12"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
@@ -3448,9 +3583,10 @@
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
-      <c r="AK28" s="13"/>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="13"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2">
@@ -3495,11 +3631,13 @@
       <c r="Q29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T29" s="12"/>
-      <c r="U29" s="1"/>
+      <c r="R29" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U29" s="12"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
@@ -3515,9 +3653,10 @@
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
-      <c r="AK29" s="13"/>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="13"/>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2">
@@ -3562,11 +3701,13 @@
       <c r="Q30" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R30" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T30" s="12"/>
-      <c r="U30" s="1"/>
+      <c r="R30" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U30" s="12"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
@@ -3582,9 +3723,10 @@
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
-      <c r="AK30" s="13"/>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="13"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2">
@@ -3629,11 +3771,13 @@
       <c r="Q31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R31" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T31" s="12"/>
-      <c r="U31" s="1"/>
+      <c r="R31" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U31" s="12"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
@@ -3649,9 +3793,10 @@
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
-      <c r="AK31" s="13"/>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="13"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2">
@@ -3696,11 +3841,13 @@
       <c r="Q32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T32" s="12"/>
-      <c r="U32" s="1"/>
+      <c r="R32" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U32" s="12"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -3716,9 +3863,10 @@
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
-      <c r="AK32" s="13"/>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="13"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2">
@@ -3763,11 +3911,13 @@
       <c r="Q33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R33" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T33" s="12"/>
-      <c r="U33" s="1"/>
+      <c r="R33" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U33" s="12"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
@@ -3783,9 +3933,10 @@
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
-      <c r="AK33" s="13"/>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="13"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2">
@@ -3830,11 +3981,13 @@
       <c r="Q34" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R34" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T34" s="12"/>
-      <c r="U34" s="1"/>
+      <c r="R34" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U34" s="12"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
@@ -3850,9 +4003,10 @@
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
-      <c r="AK34" s="13"/>
-    </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="13"/>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2">
@@ -3897,11 +4051,13 @@
       <c r="Q35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T35" s="12"/>
-      <c r="U35" s="1"/>
+      <c r="R35" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U35" s="12"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
@@ -3917,9 +4073,10 @@
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
-      <c r="AK35" s="13"/>
-    </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="13"/>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2">
@@ -3964,11 +4121,13 @@
       <c r="Q36" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T36" s="12"/>
-      <c r="U36" s="1"/>
+      <c r="R36" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U36" s="12"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
@@ -3984,9 +4143,10 @@
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
-      <c r="AK36" s="13"/>
-    </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK36" s="1"/>
+      <c r="AL36" s="13"/>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2">
@@ -4031,11 +4191,13 @@
       <c r="Q37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T37" s="12"/>
-      <c r="U37" s="1"/>
+      <c r="R37" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U37" s="12"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
@@ -4051,9 +4213,10 @@
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
-      <c r="AK37" s="13"/>
-    </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK37" s="1"/>
+      <c r="AL37" s="13"/>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2">
@@ -4098,11 +4261,13 @@
       <c r="Q38" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R38" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T38" s="12"/>
-      <c r="U38" s="1"/>
+      <c r="R38" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U38" s="12"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
@@ -4118,9 +4283,10 @@
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
-      <c r="AK38" s="13"/>
-    </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK38" s="1"/>
+      <c r="AL38" s="13"/>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2">
@@ -4165,11 +4331,13 @@
       <c r="Q39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R39" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T39" s="12"/>
-      <c r="U39" s="1"/>
+      <c r="R39" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U39" s="12"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
@@ -4185,9 +4353,10 @@
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
-      <c r="AK39" s="13"/>
-    </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK39" s="1"/>
+      <c r="AL39" s="13"/>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2">
@@ -4232,11 +4401,13 @@
       <c r="Q40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T40" s="12"/>
-      <c r="U40" s="1"/>
+      <c r="R40" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U40" s="12"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
@@ -4252,9 +4423,10 @@
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
-      <c r="AK40" s="13"/>
-    </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK40" s="1"/>
+      <c r="AL40" s="13"/>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2">
@@ -4299,11 +4471,13 @@
       <c r="Q41" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R41" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T41" s="12"/>
-      <c r="U41" s="1"/>
+      <c r="R41" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U41" s="12"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
@@ -4319,9 +4493,10 @@
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
-      <c r="AK41" s="13"/>
-    </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK41" s="1"/>
+      <c r="AL41" s="13"/>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2">
@@ -4366,11 +4541,13 @@
       <c r="Q42" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R42" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T42" s="12"/>
-      <c r="U42" s="1"/>
+      <c r="R42" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U42" s="12"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
@@ -4386,9 +4563,10 @@
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
-      <c r="AK42" s="13"/>
-    </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK42" s="1"/>
+      <c r="AL42" s="13"/>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2">
@@ -4433,11 +4611,13 @@
       <c r="Q43" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R43" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T43" s="12"/>
-      <c r="U43" s="1"/>
+      <c r="R43" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U43" s="12"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
@@ -4453,9 +4633,10 @@
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
-      <c r="AK43" s="13"/>
-    </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK43" s="1"/>
+      <c r="AL43" s="13"/>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2">
@@ -4500,11 +4681,13 @@
       <c r="Q44" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T44" s="12"/>
-      <c r="U44" s="1"/>
+      <c r="R44" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U44" s="12"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
@@ -4520,9 +4703,10 @@
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
-      <c r="AK44" s="13"/>
-    </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK44" s="1"/>
+      <c r="AL44" s="13"/>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2">
@@ -4567,11 +4751,13 @@
       <c r="Q45" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T45" s="12"/>
-      <c r="U45" s="1"/>
+      <c r="R45" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U45" s="12"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
@@ -4587,9 +4773,10 @@
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
-      <c r="AK45" s="13"/>
-    </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK45" s="1"/>
+      <c r="AL45" s="13"/>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2">
@@ -4634,11 +4821,13 @@
       <c r="Q46" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T46" s="12"/>
-      <c r="U46" s="1"/>
+      <c r="R46" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U46" s="12"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
@@ -4654,9 +4843,10 @@
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
-      <c r="AK46" s="13"/>
-    </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK46" s="1"/>
+      <c r="AL46" s="13"/>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2">
@@ -4701,11 +4891,13 @@
       <c r="Q47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R47" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T47" s="12"/>
-      <c r="U47" s="1"/>
+      <c r="R47" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U47" s="12"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
@@ -4721,9 +4913,10 @@
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
-      <c r="AK47" s="13"/>
-    </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK47" s="1"/>
+      <c r="AL47" s="13"/>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2">
@@ -4768,11 +4961,13 @@
       <c r="Q48" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T48" s="12"/>
-      <c r="U48" s="1"/>
+      <c r="R48" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U48" s="12"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
@@ -4788,9 +4983,10 @@
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
-      <c r="AK48" s="13"/>
-    </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK48" s="1"/>
+      <c r="AL48" s="13"/>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2">
@@ -4835,11 +5031,13 @@
       <c r="Q49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R49" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T49" s="12"/>
-      <c r="U49" s="1"/>
+      <c r="R49" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U49" s="12"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
@@ -4855,9 +5053,10 @@
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
-      <c r="AK49" s="13"/>
-    </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK49" s="1"/>
+      <c r="AL49" s="13"/>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2">
@@ -4902,11 +5101,13 @@
       <c r="Q50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R50" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T50" s="12"/>
-      <c r="U50" s="1"/>
+      <c r="R50" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U50" s="12"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
@@ -4922,9 +5123,10 @@
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
-      <c r="AK50" s="13"/>
-    </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK50" s="1"/>
+      <c r="AL50" s="13"/>
+    </row>
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2">
@@ -4969,11 +5171,13 @@
       <c r="Q51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R51" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T51" s="12"/>
-      <c r="U51" s="1"/>
+      <c r="R51" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U51" s="12"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -4989,9 +5193,10 @@
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
-      <c r="AK51" s="13"/>
-    </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK51" s="1"/>
+      <c r="AL51" s="13"/>
+    </row>
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2">
@@ -5036,11 +5241,13 @@
       <c r="Q52" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R52" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T52" s="12"/>
-      <c r="U52" s="1"/>
+      <c r="R52" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S52" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U52" s="12"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
@@ -5056,9 +5263,10 @@
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
-      <c r="AK52" s="13"/>
-    </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK52" s="1"/>
+      <c r="AL52" s="13"/>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2">
@@ -5103,11 +5311,13 @@
       <c r="Q53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R53" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T53" s="12"/>
-      <c r="U53" s="1"/>
+      <c r="R53" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U53" s="12"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
@@ -5123,9 +5333,10 @@
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
-      <c r="AK53" s="13"/>
-    </row>
-    <row r="54" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK53" s="1"/>
+      <c r="AL53" s="13"/>
+    </row>
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2">
@@ -5170,11 +5381,13 @@
       <c r="Q54" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R54" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T54" s="12"/>
-      <c r="U54" s="1"/>
+      <c r="R54" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S54" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U54" s="12"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
@@ -5190,9 +5403,10 @@
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
-      <c r="AK54" s="13"/>
-    </row>
-    <row r="55" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK54" s="1"/>
+      <c r="AL54" s="13"/>
+    </row>
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2">
@@ -5237,11 +5451,13 @@
       <c r="Q55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R55" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T55" s="12"/>
-      <c r="U55" s="1"/>
+      <c r="R55" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S55" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U55" s="12"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
@@ -5257,9 +5473,10 @@
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
-      <c r="AK55" s="13"/>
-    </row>
-    <row r="56" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK55" s="1"/>
+      <c r="AL55" s="13"/>
+    </row>
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2">
@@ -5304,11 +5521,13 @@
       <c r="Q56" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R56" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T56" s="12"/>
-      <c r="U56" s="1"/>
+      <c r="R56" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S56" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U56" s="12"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
@@ -5324,9 +5543,10 @@
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
-      <c r="AK56" s="13"/>
-    </row>
-    <row r="57" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK56" s="1"/>
+      <c r="AL56" s="13"/>
+    </row>
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2">
@@ -5371,11 +5591,13 @@
       <c r="Q57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R57" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T57" s="12"/>
-      <c r="U57" s="1"/>
+      <c r="R57" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U57" s="12"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
@@ -5391,9 +5613,10 @@
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
-      <c r="AK57" s="13"/>
-    </row>
-    <row r="58" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK57" s="1"/>
+      <c r="AL57" s="13"/>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2">
@@ -5438,11 +5661,13 @@
       <c r="Q58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R58" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T58" s="12"/>
-      <c r="U58" s="1"/>
+      <c r="R58" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S58" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U58" s="12"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
@@ -5458,9 +5683,10 @@
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
-      <c r="AK58" s="13"/>
-    </row>
-    <row r="59" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK58" s="1"/>
+      <c r="AL58" s="13"/>
+    </row>
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2">
@@ -5505,11 +5731,13 @@
       <c r="Q59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R59" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T59" s="12"/>
-      <c r="U59" s="1"/>
+      <c r="R59" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U59" s="12"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
@@ -5525,9 +5753,10 @@
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
-      <c r="AK59" s="13"/>
-    </row>
-    <row r="60" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK59" s="1"/>
+      <c r="AL59" s="13"/>
+    </row>
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2">
@@ -5572,11 +5801,13 @@
       <c r="Q60" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R60" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T60" s="12"/>
-      <c r="U60" s="1"/>
+      <c r="R60" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S60" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U60" s="12"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
@@ -5592,9 +5823,10 @@
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
-      <c r="AK60" s="13"/>
-    </row>
-    <row r="61" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK60" s="1"/>
+      <c r="AL60" s="13"/>
+    </row>
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2">
@@ -5639,11 +5871,13 @@
       <c r="Q61" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R61" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T61" s="12"/>
-      <c r="U61" s="1"/>
+      <c r="R61" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U61" s="12"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
@@ -5659,9 +5893,10 @@
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
-      <c r="AK61" s="13"/>
-    </row>
-    <row r="62" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK61" s="1"/>
+      <c r="AL61" s="13"/>
+    </row>
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2">
@@ -5706,11 +5941,13 @@
       <c r="Q62" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R62" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T62" s="12"/>
-      <c r="U62" s="1"/>
+      <c r="R62" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S62" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U62" s="12"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
@@ -5726,9 +5963,10 @@
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
-      <c r="AK62" s="13"/>
-    </row>
-    <row r="63" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK62" s="1"/>
+      <c r="AL62" s="13"/>
+    </row>
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2">
@@ -5773,11 +6011,13 @@
       <c r="Q63" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R63" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T63" s="12"/>
-      <c r="U63" s="1"/>
+      <c r="R63" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U63" s="12"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
@@ -5793,9 +6033,10 @@
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
-      <c r="AK63" s="13"/>
-    </row>
-    <row r="64" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK63" s="1"/>
+      <c r="AL63" s="13"/>
+    </row>
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2">
@@ -5840,11 +6081,13 @@
       <c r="Q64" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R64" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T64" s="12"/>
-      <c r="U64" s="1"/>
+      <c r="R64" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S64" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U64" s="12"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
@@ -5860,9 +6103,10 @@
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
-      <c r="AK64" s="13"/>
-    </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK64" s="1"/>
+      <c r="AL64" s="13"/>
+    </row>
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2">
@@ -5907,11 +6151,13 @@
       <c r="Q65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R65" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T65" s="12"/>
-      <c r="U65" s="1"/>
+      <c r="R65" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S65" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U65" s="12"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
@@ -5927,9 +6173,10 @@
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
-      <c r="AK65" s="13"/>
-    </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK65" s="1"/>
+      <c r="AL65" s="13"/>
+    </row>
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2">
@@ -5974,11 +6221,13 @@
       <c r="Q66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R66" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T66" s="12"/>
-      <c r="U66" s="1"/>
+      <c r="R66" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S66" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U66" s="12"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
       <c r="X66" s="1"/>
@@ -5994,9 +6243,10 @@
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
-      <c r="AK66" s="13"/>
-    </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK66" s="1"/>
+      <c r="AL66" s="13"/>
+    </row>
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2">
@@ -6041,11 +6291,13 @@
       <c r="Q67" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R67" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T67" s="12"/>
-      <c r="U67" s="1"/>
+      <c r="R67" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U67" s="12"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
@@ -6061,9 +6313,10 @@
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
-      <c r="AK67" s="13"/>
-    </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK67" s="1"/>
+      <c r="AL67" s="13"/>
+    </row>
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2">
@@ -6108,11 +6361,13 @@
       <c r="Q68" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R68" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T68" s="12"/>
-      <c r="U68" s="1"/>
+      <c r="R68" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S68" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U68" s="12"/>
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
@@ -6128,9 +6383,10 @@
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
-      <c r="AK68" s="13"/>
-    </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK68" s="1"/>
+      <c r="AL68" s="13"/>
+    </row>
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2">
@@ -6175,11 +6431,13 @@
       <c r="Q69" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R69" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T69" s="12"/>
-      <c r="U69" s="1"/>
+      <c r="R69" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U69" s="12"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
@@ -6195,9 +6453,10 @@
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
-      <c r="AK69" s="13"/>
-    </row>
-    <row r="70" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK69" s="1"/>
+      <c r="AL69" s="13"/>
+    </row>
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2">
@@ -6242,11 +6501,13 @@
       <c r="Q70" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R70" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T70" s="12"/>
-      <c r="U70" s="1"/>
+      <c r="R70" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S70" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U70" s="12"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
@@ -6262,9 +6523,10 @@
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
-      <c r="AK70" s="13"/>
-    </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK70" s="1"/>
+      <c r="AL70" s="13"/>
+    </row>
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2">
@@ -6309,11 +6571,13 @@
       <c r="Q71" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R71" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T71" s="12"/>
-      <c r="U71" s="1"/>
+      <c r="R71" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U71" s="12"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
@@ -6329,9 +6593,10 @@
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
-      <c r="AK71" s="13"/>
-    </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK71" s="1"/>
+      <c r="AL71" s="13"/>
+    </row>
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2">
@@ -6376,11 +6641,13 @@
       <c r="Q72" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R72" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T72" s="12"/>
-      <c r="U72" s="1"/>
+      <c r="R72" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U72" s="12"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
       <c r="X72" s="1"/>
@@ -6396,9 +6663,10 @@
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
-      <c r="AK72" s="13"/>
-    </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK72" s="1"/>
+      <c r="AL72" s="13"/>
+    </row>
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2">
@@ -6443,11 +6711,13 @@
       <c r="Q73" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R73" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T73" s="12"/>
-      <c r="U73" s="1"/>
+      <c r="R73" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U73" s="12"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
@@ -6463,9 +6733,10 @@
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
-      <c r="AK73" s="13"/>
-    </row>
-    <row r="74" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK73" s="1"/>
+      <c r="AL73" s="13"/>
+    </row>
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2">
@@ -6510,11 +6781,13 @@
       <c r="Q74" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R74" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T74" s="12"/>
-      <c r="U74" s="1"/>
+      <c r="R74" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S74" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U74" s="12"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
@@ -6530,9 +6803,10 @@
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
-      <c r="AK74" s="13"/>
-    </row>
-    <row r="75" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK74" s="1"/>
+      <c r="AL74" s="13"/>
+    </row>
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2">
@@ -6577,11 +6851,13 @@
       <c r="Q75" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R75" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T75" s="12"/>
-      <c r="U75" s="1"/>
+      <c r="R75" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U75" s="12"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
@@ -6597,9 +6873,10 @@
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
-      <c r="AK75" s="13"/>
-    </row>
-    <row r="76" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK75" s="1"/>
+      <c r="AL75" s="13"/>
+    </row>
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2">
@@ -6644,11 +6921,13 @@
       <c r="Q76" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R76" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T76" s="12"/>
-      <c r="U76" s="1"/>
+      <c r="R76" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S76" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U76" s="12"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
@@ -6664,9 +6943,10 @@
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
-      <c r="AK76" s="13"/>
-    </row>
-    <row r="77" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK76" s="1"/>
+      <c r="AL76" s="13"/>
+    </row>
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2">
@@ -6711,11 +6991,13 @@
       <c r="Q77" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R77" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T77" s="12"/>
-      <c r="U77" s="1"/>
+      <c r="R77" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U77" s="12"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
       <c r="X77" s="1"/>
@@ -6731,9 +7013,10 @@
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
-      <c r="AK77" s="13"/>
-    </row>
-    <row r="78" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK77" s="1"/>
+      <c r="AL77" s="13"/>
+    </row>
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2">
@@ -6778,11 +7061,13 @@
       <c r="Q78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R78" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T78" s="12"/>
-      <c r="U78" s="1"/>
+      <c r="R78" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S78" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U78" s="12"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
       <c r="X78" s="1"/>
@@ -6798,9 +7083,10 @@
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
-      <c r="AK78" s="13"/>
-    </row>
-    <row r="79" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK78" s="1"/>
+      <c r="AL78" s="13"/>
+    </row>
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2">
@@ -6845,11 +7131,13 @@
       <c r="Q79" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R79" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T79" s="12"/>
-      <c r="U79" s="1"/>
+      <c r="R79" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U79" s="12"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
       <c r="X79" s="1"/>
@@ -6865,9 +7153,10 @@
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
-      <c r="AK79" s="13"/>
-    </row>
-    <row r="80" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK79" s="1"/>
+      <c r="AL79" s="13"/>
+    </row>
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2">
@@ -6912,11 +7201,13 @@
       <c r="Q80" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R80" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T80" s="12"/>
-      <c r="U80" s="1"/>
+      <c r="R80" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S80" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U80" s="12"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
@@ -6932,9 +7223,10 @@
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
-      <c r="AK80" s="13"/>
-    </row>
-    <row r="81" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK80" s="1"/>
+      <c r="AL80" s="13"/>
+    </row>
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2">
@@ -6979,11 +7271,13 @@
       <c r="Q81" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R81" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T81" s="12"/>
-      <c r="U81" s="1"/>
+      <c r="R81" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U81" s="12"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
@@ -6999,9 +7293,10 @@
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
-      <c r="AK81" s="13"/>
-    </row>
-    <row r="82" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK81" s="1"/>
+      <c r="AL81" s="13"/>
+    </row>
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2">
@@ -7046,11 +7341,13 @@
       <c r="Q82" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R82" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T82" s="12"/>
-      <c r="U82" s="1"/>
+      <c r="R82" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S82" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U82" s="12"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
@@ -7066,9 +7363,10 @@
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
-      <c r="AK82" s="13"/>
-    </row>
-    <row r="83" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK82" s="1"/>
+      <c r="AL82" s="13"/>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2">
@@ -7113,11 +7411,13 @@
       <c r="Q83" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R83" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T83" s="12"/>
-      <c r="U83" s="1"/>
+      <c r="R83" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U83" s="12"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
       <c r="X83" s="1"/>
@@ -7133,9 +7433,10 @@
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
-      <c r="AK83" s="13"/>
-    </row>
-    <row r="84" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK83" s="1"/>
+      <c r="AL83" s="13"/>
+    </row>
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2">
@@ -7180,11 +7481,13 @@
       <c r="Q84" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R84" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T84" s="12"/>
-      <c r="U84" s="1"/>
+      <c r="R84" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U84" s="12"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
       <c r="X84" s="1"/>
@@ -7200,9 +7503,10 @@
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
-      <c r="AK84" s="13"/>
-    </row>
-    <row r="85" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK84" s="1"/>
+      <c r="AL84" s="13"/>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2">
@@ -7247,11 +7551,13 @@
       <c r="Q85" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R85" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T85" s="12"/>
-      <c r="U85" s="1"/>
+      <c r="R85" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U85" s="12"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
@@ -7267,9 +7573,10 @@
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
-      <c r="AK85" s="13"/>
-    </row>
-    <row r="86" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK85" s="1"/>
+      <c r="AL85" s="13"/>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2">
@@ -7314,11 +7621,13 @@
       <c r="Q86" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R86" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T86" s="12"/>
-      <c r="U86" s="1"/>
+      <c r="R86" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S86" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U86" s="12"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
@@ -7334,9 +7643,10 @@
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
-      <c r="AK86" s="13"/>
-    </row>
-    <row r="87" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK86" s="1"/>
+      <c r="AL86" s="13"/>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2">
@@ -7381,11 +7691,13 @@
       <c r="Q87" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R87" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T87" s="12"/>
-      <c r="U87" s="1"/>
+      <c r="R87" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U87" s="12"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
@@ -7401,9 +7713,10 @@
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
-      <c r="AK87" s="13"/>
-    </row>
-    <row r="88" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK87" s="1"/>
+      <c r="AL87" s="13"/>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2">
@@ -7448,11 +7761,13 @@
       <c r="Q88" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R88" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T88" s="12"/>
-      <c r="U88" s="1"/>
+      <c r="R88" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U88" s="12"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
@@ -7468,9 +7783,10 @@
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
-      <c r="AK88" s="13"/>
-    </row>
-    <row r="89" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK88" s="1"/>
+      <c r="AL88" s="13"/>
+    </row>
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2">
@@ -7515,11 +7831,13 @@
       <c r="Q89" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R89" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T89" s="12"/>
-      <c r="U89" s="1"/>
+      <c r="R89" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U89" s="12"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
@@ -7535,9 +7853,10 @@
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
-      <c r="AK89" s="13"/>
-    </row>
-    <row r="90" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK89" s="1"/>
+      <c r="AL89" s="13"/>
+    </row>
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2">
@@ -7582,11 +7901,13 @@
       <c r="Q90" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R90" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T90" s="12"/>
-      <c r="U90" s="1"/>
+      <c r="R90" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U90" s="12"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
@@ -7602,9 +7923,10 @@
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
-      <c r="AK90" s="13"/>
-    </row>
-    <row r="91" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK90" s="1"/>
+      <c r="AL90" s="13"/>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2">
@@ -7649,11 +7971,13 @@
       <c r="Q91" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R91" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T91" s="12"/>
-      <c r="U91" s="1"/>
+      <c r="R91" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U91" s="12"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
       <c r="X91" s="1"/>
@@ -7669,9 +7993,10 @@
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
-      <c r="AK91" s="13"/>
-    </row>
-    <row r="92" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK91" s="1"/>
+      <c r="AL91" s="13"/>
+    </row>
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2">
@@ -7716,11 +8041,13 @@
       <c r="Q92" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R92" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T92" s="12"/>
-      <c r="U92" s="1"/>
+      <c r="R92" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="S92" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U92" s="12"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
       <c r="X92" s="1"/>
@@ -7736,9 +8063,10 @@
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
-      <c r="AK92" s="13"/>
-    </row>
-    <row r="93" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK92" s="1"/>
+      <c r="AL92" s="13"/>
+    </row>
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2">
@@ -7783,11 +8111,13 @@
       <c r="Q93" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R93" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T93" s="12"/>
-      <c r="U93" s="1"/>
+      <c r="R93" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U93" s="12"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
       <c r="X93" s="1"/>
@@ -7803,9 +8133,10 @@
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
-      <c r="AK93" s="13"/>
-    </row>
-    <row r="94" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK93" s="1"/>
+      <c r="AL93" s="13"/>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2">
@@ -7850,11 +8181,13 @@
       <c r="Q94" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R94" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T94" s="12"/>
-      <c r="U94" s="1"/>
+      <c r="R94" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U94" s="12"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
       <c r="X94" s="1"/>
@@ -7870,9 +8203,10 @@
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
-      <c r="AK94" s="13"/>
-    </row>
-    <row r="95" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK94" s="1"/>
+      <c r="AL94" s="13"/>
+    </row>
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2">
@@ -7917,11 +8251,13 @@
       <c r="Q95" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R95" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T95" s="12"/>
-      <c r="U95" s="1"/>
+      <c r="R95" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U95" s="12"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
       <c r="X95" s="1"/>
@@ -7937,9 +8273,10 @@
       <c r="AH95" s="1"/>
       <c r="AI95" s="1"/>
       <c r="AJ95" s="1"/>
-      <c r="AK95" s="13"/>
-    </row>
-    <row r="96" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK95" s="1"/>
+      <c r="AL95" s="13"/>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2">
@@ -7984,11 +8321,13 @@
       <c r="Q96" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R96" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T96" s="12"/>
-      <c r="U96" s="1"/>
+      <c r="R96" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U96" s="12"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
       <c r="X96" s="1"/>
@@ -8004,9 +8343,10 @@
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
       <c r="AJ96" s="1"/>
-      <c r="AK96" s="13"/>
-    </row>
-    <row r="97" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK96" s="1"/>
+      <c r="AL96" s="13"/>
+    </row>
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2">
@@ -8051,11 +8391,13 @@
       <c r="Q97" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T97" s="12"/>
-      <c r="U97" s="1"/>
+      <c r="R97" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U97" s="12"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
       <c r="X97" s="1"/>
@@ -8071,9 +8413,10 @@
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1"/>
-      <c r="AK97" s="13"/>
-    </row>
-    <row r="98" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK97" s="1"/>
+      <c r="AL97" s="13"/>
+    </row>
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2">
@@ -8118,11 +8461,13 @@
       <c r="Q98" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T98" s="12"/>
-      <c r="U98" s="1"/>
+      <c r="R98" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U98" s="12"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
       <c r="X98" s="1"/>
@@ -8138,9 +8483,10 @@
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
       <c r="AJ98" s="1"/>
-      <c r="AK98" s="13"/>
-    </row>
-    <row r="99" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK98" s="1"/>
+      <c r="AL98" s="13"/>
+    </row>
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2">
@@ -8185,11 +8531,13 @@
       <c r="Q99" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R99" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T99" s="12"/>
-      <c r="U99" s="1"/>
+      <c r="R99" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U99" s="12"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
       <c r="X99" s="1"/>
@@ -8205,9 +8553,10 @@
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
       <c r="AJ99" s="1"/>
-      <c r="AK99" s="13"/>
-    </row>
-    <row r="100" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK99" s="1"/>
+      <c r="AL99" s="13"/>
+    </row>
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2">
@@ -8252,11 +8601,13 @@
       <c r="Q100" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R100" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T100" s="12"/>
-      <c r="U100" s="1"/>
+      <c r="R100" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U100" s="12"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
       <c r="X100" s="1"/>
@@ -8272,9 +8623,10 @@
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
       <c r="AJ100" s="1"/>
-      <c r="AK100" s="13"/>
-    </row>
-    <row r="101" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK100" s="1"/>
+      <c r="AL100" s="13"/>
+    </row>
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2">
@@ -8319,11 +8671,13 @@
       <c r="Q101" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R101" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T101" s="12"/>
-      <c r="U101" s="1"/>
+      <c r="R101" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U101" s="12"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
       <c r="X101" s="1"/>
@@ -8339,9 +8693,10 @@
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1"/>
-      <c r="AK101" s="13"/>
-    </row>
-    <row r="102" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK101" s="1"/>
+      <c r="AL101" s="13"/>
+    </row>
+    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2">
@@ -8386,11 +8741,13 @@
       <c r="Q102" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R102" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T102" s="12"/>
-      <c r="U102" s="1"/>
+      <c r="R102" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U102" s="12"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
       <c r="X102" s="1"/>
@@ -8406,9 +8763,10 @@
       <c r="AH102" s="1"/>
       <c r="AI102" s="1"/>
       <c r="AJ102" s="1"/>
-      <c r="AK102" s="13"/>
-    </row>
-    <row r="103" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK102" s="1"/>
+      <c r="AL102" s="13"/>
+    </row>
+    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2">
@@ -8453,11 +8811,13 @@
       <c r="Q103" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R103" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T103" s="12"/>
-      <c r="U103" s="1"/>
+      <c r="R103" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U103" s="12"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
       <c r="X103" s="1"/>
@@ -8473,9 +8833,10 @@
       <c r="AH103" s="1"/>
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1"/>
-      <c r="AK103" s="13"/>
-    </row>
-    <row r="104" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK103" s="1"/>
+      <c r="AL103" s="13"/>
+    </row>
+    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2">
@@ -8520,11 +8881,13 @@
       <c r="Q104" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R104" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T104" s="12"/>
-      <c r="U104" s="1"/>
+      <c r="R104" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U104" s="12"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
@@ -8540,9 +8903,10 @@
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1"/>
-      <c r="AK104" s="13"/>
-    </row>
-    <row r="105" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK104" s="1"/>
+      <c r="AL104" s="13"/>
+    </row>
+    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2">
@@ -8587,11 +8951,13 @@
       <c r="Q105" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R105" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T105" s="12"/>
-      <c r="U105" s="1"/>
+      <c r="R105" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U105" s="12"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
       <c r="X105" s="1"/>
@@ -8607,9 +8973,10 @@
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
-      <c r="AK105" s="13"/>
-    </row>
-    <row r="106" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK105" s="1"/>
+      <c r="AL105" s="13"/>
+    </row>
+    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2">
@@ -8654,11 +9021,13 @@
       <c r="Q106" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R106" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T106" s="12"/>
-      <c r="U106" s="1"/>
+      <c r="R106" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U106" s="12"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
       <c r="X106" s="1"/>
@@ -8674,9 +9043,10 @@
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1"/>
-      <c r="AK106" s="13"/>
-    </row>
-    <row r="107" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK106" s="1"/>
+      <c r="AL106" s="13"/>
+    </row>
+    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2">
@@ -8721,11 +9091,13 @@
       <c r="Q107" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R107" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T107" s="12"/>
-      <c r="U107" s="1"/>
+      <c r="R107" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S107" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U107" s="12"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
       <c r="X107" s="1"/>
@@ -8741,9 +9113,10 @@
       <c r="AH107" s="1"/>
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1"/>
-      <c r="AK107" s="13"/>
-    </row>
-    <row r="108" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK107" s="1"/>
+      <c r="AL107" s="13"/>
+    </row>
+    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2">
@@ -8788,11 +9161,13 @@
       <c r="Q108" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R108" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T108" s="12"/>
-      <c r="U108" s="1"/>
+      <c r="R108" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S108" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U108" s="12"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
       <c r="X108" s="1"/>
@@ -8808,9 +9183,10 @@
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1"/>
-      <c r="AK108" s="13"/>
-    </row>
-    <row r="109" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK108" s="1"/>
+      <c r="AL108" s="13"/>
+    </row>
+    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2">
@@ -8855,11 +9231,13 @@
       <c r="Q109" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R109" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T109" s="12"/>
-      <c r="U109" s="1"/>
+      <c r="R109" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U109" s="12"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
       <c r="X109" s="1"/>
@@ -8875,9 +9253,10 @@
       <c r="AH109" s="1"/>
       <c r="AI109" s="1"/>
       <c r="AJ109" s="1"/>
-      <c r="AK109" s="13"/>
-    </row>
-    <row r="110" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK109" s="1"/>
+      <c r="AL109" s="13"/>
+    </row>
+    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2">
@@ -8922,11 +9301,13 @@
       <c r="Q110" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R110" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T110" s="12"/>
-      <c r="U110" s="1"/>
+      <c r="R110" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U110" s="12"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
       <c r="X110" s="1"/>
@@ -8942,9 +9323,10 @@
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1"/>
-      <c r="AK110" s="13"/>
-    </row>
-    <row r="111" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK110" s="1"/>
+      <c r="AL110" s="13"/>
+    </row>
+    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2">
@@ -8989,11 +9371,13 @@
       <c r="Q111" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R111" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T111" s="12"/>
-      <c r="U111" s="1"/>
+      <c r="R111" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S111" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U111" s="12"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
       <c r="X111" s="1"/>
@@ -9009,9 +9393,10 @@
       <c r="AH111" s="1"/>
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1"/>
-      <c r="AK111" s="13"/>
-    </row>
-    <row r="112" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK111" s="1"/>
+      <c r="AL111" s="13"/>
+    </row>
+    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2">
@@ -9056,11 +9441,13 @@
       <c r="Q112" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R112" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T112" s="12"/>
-      <c r="U112" s="1"/>
+      <c r="R112" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U112" s="12"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
       <c r="X112" s="1"/>
@@ -9076,9 +9463,10 @@
       <c r="AH112" s="1"/>
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1"/>
-      <c r="AK112" s="13"/>
-    </row>
-    <row r="113" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK112" s="1"/>
+      <c r="AL112" s="13"/>
+    </row>
+    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2">
@@ -9123,11 +9511,13 @@
       <c r="Q113" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R113" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T113" s="12"/>
-      <c r="U113" s="1"/>
+      <c r="R113" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U113" s="12"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
       <c r="X113" s="1"/>
@@ -9143,9 +9533,10 @@
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
       <c r="AJ113" s="1"/>
-      <c r="AK113" s="13"/>
-    </row>
-    <row r="114" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK113" s="1"/>
+      <c r="AL113" s="13"/>
+    </row>
+    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2">
@@ -9190,11 +9581,13 @@
       <c r="Q114" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R114" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T114" s="12"/>
-      <c r="U114" s="1"/>
+      <c r="R114" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S114" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U114" s="12"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
@@ -9210,9 +9603,10 @@
       <c r="AH114" s="1"/>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1"/>
-      <c r="AK114" s="13"/>
-    </row>
-    <row r="115" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK114" s="1"/>
+      <c r="AL114" s="13"/>
+    </row>
+    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2">
@@ -9257,11 +9651,13 @@
       <c r="Q115" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R115" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T115" s="12"/>
-      <c r="U115" s="1"/>
+      <c r="R115" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S115" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U115" s="12"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
@@ -9277,9 +9673,10 @@
       <c r="AH115" s="1"/>
       <c r="AI115" s="1"/>
       <c r="AJ115" s="1"/>
-      <c r="AK115" s="13"/>
-    </row>
-    <row r="116" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK115" s="1"/>
+      <c r="AL115" s="13"/>
+    </row>
+    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2">
@@ -9324,11 +9721,13 @@
       <c r="Q116" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R116" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T116" s="12"/>
-      <c r="U116" s="1"/>
+      <c r="R116" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U116" s="12"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
@@ -9344,9 +9743,10 @@
       <c r="AH116" s="1"/>
       <c r="AI116" s="1"/>
       <c r="AJ116" s="1"/>
-      <c r="AK116" s="13"/>
-    </row>
-    <row r="117" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK116" s="1"/>
+      <c r="AL116" s="13"/>
+    </row>
+    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2">
@@ -9391,11 +9791,13 @@
       <c r="Q117" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R117" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T117" s="12"/>
-      <c r="U117" s="1"/>
+      <c r="R117" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S117" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U117" s="12"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
@@ -9411,9 +9813,10 @@
       <c r="AH117" s="1"/>
       <c r="AI117" s="1"/>
       <c r="AJ117" s="1"/>
-      <c r="AK117" s="13"/>
-    </row>
-    <row r="118" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK117" s="1"/>
+      <c r="AL117" s="13"/>
+    </row>
+    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2">
@@ -9458,11 +9861,13 @@
       <c r="Q118" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R118" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T118" s="12"/>
-      <c r="U118" s="1"/>
+      <c r="R118" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S118" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U118" s="12"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
       <c r="X118" s="1"/>
@@ -9478,9 +9883,10 @@
       <c r="AH118" s="1"/>
       <c r="AI118" s="1"/>
       <c r="AJ118" s="1"/>
-      <c r="AK118" s="13"/>
-    </row>
-    <row r="119" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK118" s="1"/>
+      <c r="AL118" s="13"/>
+    </row>
+    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2">
@@ -9525,11 +9931,13 @@
       <c r="Q119" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R119" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T119" s="12"/>
-      <c r="U119" s="1"/>
+      <c r="R119" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S119" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U119" s="12"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
       <c r="X119" s="1"/>
@@ -9545,9 +9953,10 @@
       <c r="AH119" s="1"/>
       <c r="AI119" s="1"/>
       <c r="AJ119" s="1"/>
-      <c r="AK119" s="13"/>
-    </row>
-    <row r="120" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK119" s="1"/>
+      <c r="AL119" s="13"/>
+    </row>
+    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2">
@@ -9592,11 +10001,13 @@
       <c r="Q120" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R120" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T120" s="12"/>
-      <c r="U120" s="1"/>
+      <c r="R120" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S120" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U120" s="12"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
       <c r="X120" s="1"/>
@@ -9612,9 +10023,10 @@
       <c r="AH120" s="1"/>
       <c r="AI120" s="1"/>
       <c r="AJ120" s="1"/>
-      <c r="AK120" s="13"/>
-    </row>
-    <row r="121" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK120" s="1"/>
+      <c r="AL120" s="13"/>
+    </row>
+    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2">
@@ -9659,11 +10071,13 @@
       <c r="Q121" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R121" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T121" s="12"/>
-      <c r="U121" s="1"/>
+      <c r="R121" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S121" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U121" s="12"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
       <c r="X121" s="1"/>
@@ -9679,9 +10093,10 @@
       <c r="AH121" s="1"/>
       <c r="AI121" s="1"/>
       <c r="AJ121" s="1"/>
-      <c r="AK121" s="13"/>
-    </row>
-    <row r="122" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK121" s="1"/>
+      <c r="AL121" s="13"/>
+    </row>
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2">
@@ -9726,11 +10141,13 @@
       <c r="Q122" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R122" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T122" s="12"/>
-      <c r="U122" s="1"/>
+      <c r="R122" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S122" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U122" s="12"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
       <c r="X122" s="1"/>
@@ -9746,9 +10163,10 @@
       <c r="AH122" s="1"/>
       <c r="AI122" s="1"/>
       <c r="AJ122" s="1"/>
-      <c r="AK122" s="13"/>
-    </row>
-    <row r="123" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK122" s="1"/>
+      <c r="AL122" s="13"/>
+    </row>
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2">
@@ -9793,11 +10211,13 @@
       <c r="Q123" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R123" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T123" s="12"/>
-      <c r="U123" s="1"/>
+      <c r="R123" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S123" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U123" s="12"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
       <c r="X123" s="1"/>
@@ -9813,9 +10233,10 @@
       <c r="AH123" s="1"/>
       <c r="AI123" s="1"/>
       <c r="AJ123" s="1"/>
-      <c r="AK123" s="13"/>
-    </row>
-    <row r="124" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK123" s="1"/>
+      <c r="AL123" s="13"/>
+    </row>
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2">
@@ -9860,11 +10281,13 @@
       <c r="Q124" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R124" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T124" s="12"/>
-      <c r="U124" s="1"/>
+      <c r="R124" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S124" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U124" s="12"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
       <c r="X124" s="1"/>
@@ -9880,9 +10303,10 @@
       <c r="AH124" s="1"/>
       <c r="AI124" s="1"/>
       <c r="AJ124" s="1"/>
-      <c r="AK124" s="13"/>
-    </row>
-    <row r="125" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK124" s="1"/>
+      <c r="AL124" s="13"/>
+    </row>
+    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2">
@@ -9927,11 +10351,13 @@
       <c r="Q125" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R125" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T125" s="12"/>
-      <c r="U125" s="1"/>
+      <c r="R125" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S125" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U125" s="12"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
       <c r="X125" s="1"/>
@@ -9947,9 +10373,10 @@
       <c r="AH125" s="1"/>
       <c r="AI125" s="1"/>
       <c r="AJ125" s="1"/>
-      <c r="AK125" s="13"/>
-    </row>
-    <row r="126" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK125" s="1"/>
+      <c r="AL125" s="13"/>
+    </row>
+    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2">
@@ -9994,11 +10421,13 @@
       <c r="Q126" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R126" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T126" s="12"/>
-      <c r="U126" s="1"/>
+      <c r="R126" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S126" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U126" s="12"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
       <c r="X126" s="1"/>
@@ -10014,9 +10443,10 @@
       <c r="AH126" s="1"/>
       <c r="AI126" s="1"/>
       <c r="AJ126" s="1"/>
-      <c r="AK126" s="13"/>
-    </row>
-    <row r="127" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK126" s="1"/>
+      <c r="AL126" s="13"/>
+    </row>
+    <row r="127" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2">
@@ -10061,11 +10491,13 @@
       <c r="Q127" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R127" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T127" s="12"/>
-      <c r="U127" s="1"/>
+      <c r="R127" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S127" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U127" s="12"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
       <c r="X127" s="1"/>
@@ -10081,9 +10513,10 @@
       <c r="AH127" s="1"/>
       <c r="AI127" s="1"/>
       <c r="AJ127" s="1"/>
-      <c r="AK127" s="13"/>
-    </row>
-    <row r="128" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK127" s="1"/>
+      <c r="AL127" s="13"/>
+    </row>
+    <row r="128" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2">
@@ -10128,11 +10561,13 @@
       <c r="Q128" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R128" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T128" s="12"/>
-      <c r="U128" s="1"/>
+      <c r="R128" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S128" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U128" s="12"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
       <c r="X128" s="1"/>
@@ -10148,9 +10583,10 @@
       <c r="AH128" s="1"/>
       <c r="AI128" s="1"/>
       <c r="AJ128" s="1"/>
-      <c r="AK128" s="13"/>
-    </row>
-    <row r="129" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK128" s="1"/>
+      <c r="AL128" s="13"/>
+    </row>
+    <row r="129" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2">
@@ -10195,11 +10631,13 @@
       <c r="Q129" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R129" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T129" s="12"/>
-      <c r="U129" s="1"/>
+      <c r="R129" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S129" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U129" s="12"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
       <c r="X129" s="1"/>
@@ -10215,9 +10653,10 @@
       <c r="AH129" s="1"/>
       <c r="AI129" s="1"/>
       <c r="AJ129" s="1"/>
-      <c r="AK129" s="13"/>
-    </row>
-    <row r="130" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK129" s="1"/>
+      <c r="AL129" s="13"/>
+    </row>
+    <row r="130" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2">
@@ -10262,11 +10701,13 @@
       <c r="Q130" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R130" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T130" s="12"/>
-      <c r="U130" s="1"/>
+      <c r="R130" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S130" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U130" s="12"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
       <c r="X130" s="1"/>
@@ -10282,9 +10723,10 @@
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
-      <c r="AK130" s="13"/>
-    </row>
-    <row r="131" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK130" s="1"/>
+      <c r="AL130" s="13"/>
+    </row>
+    <row r="131" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2">
@@ -10329,11 +10771,13 @@
       <c r="Q131" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R131" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T131" s="12"/>
-      <c r="U131" s="1"/>
+      <c r="R131" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S131" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U131" s="12"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
       <c r="X131" s="1"/>
@@ -10349,9 +10793,10 @@
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1"/>
-      <c r="AK131" s="13"/>
-    </row>
-    <row r="132" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK131" s="1"/>
+      <c r="AL131" s="13"/>
+    </row>
+    <row r="132" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2">
@@ -10396,11 +10841,13 @@
       <c r="Q132" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R132" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T132" s="12"/>
-      <c r="U132" s="1"/>
+      <c r="R132" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S132" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U132" s="12"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
       <c r="X132" s="1"/>
@@ -10416,9 +10863,10 @@
       <c r="AH132" s="1"/>
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1"/>
-      <c r="AK132" s="13"/>
-    </row>
-    <row r="133" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK132" s="1"/>
+      <c r="AL132" s="13"/>
+    </row>
+    <row r="133" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2">
@@ -10463,11 +10911,13 @@
       <c r="Q133" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R133" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T133" s="12"/>
-      <c r="U133" s="1"/>
+      <c r="R133" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S133" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U133" s="12"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
       <c r="X133" s="1"/>
@@ -10483,9 +10933,10 @@
       <c r="AH133" s="1"/>
       <c r="AI133" s="1"/>
       <c r="AJ133" s="1"/>
-      <c r="AK133" s="13"/>
-    </row>
-    <row r="134" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK133" s="1"/>
+      <c r="AL133" s="13"/>
+    </row>
+    <row r="134" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2">
@@ -10530,11 +10981,13 @@
       <c r="Q134" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R134" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T134" s="12"/>
-      <c r="U134" s="1"/>
+      <c r="R134" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S134" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U134" s="12"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
       <c r="X134" s="1"/>
@@ -10550,9 +11003,10 @@
       <c r="AH134" s="1"/>
       <c r="AI134" s="1"/>
       <c r="AJ134" s="1"/>
-      <c r="AK134" s="13"/>
-    </row>
-    <row r="135" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK134" s="1"/>
+      <c r="AL134" s="13"/>
+    </row>
+    <row r="135" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2">
@@ -10597,11 +11051,13 @@
       <c r="Q135" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R135" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T135" s="12"/>
-      <c r="U135" s="1"/>
+      <c r="R135" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S135" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U135" s="12"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
       <c r="X135" s="1"/>
@@ -10617,9 +11073,10 @@
       <c r="AH135" s="1"/>
       <c r="AI135" s="1"/>
       <c r="AJ135" s="1"/>
-      <c r="AK135" s="13"/>
-    </row>
-    <row r="136" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK135" s="1"/>
+      <c r="AL135" s="13"/>
+    </row>
+    <row r="136" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2">
@@ -10664,11 +11121,13 @@
       <c r="Q136" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R136" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T136" s="12"/>
-      <c r="U136" s="1"/>
+      <c r="R136" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S136" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U136" s="12"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
       <c r="X136" s="1"/>
@@ -10684,9 +11143,10 @@
       <c r="AH136" s="1"/>
       <c r="AI136" s="1"/>
       <c r="AJ136" s="1"/>
-      <c r="AK136" s="13"/>
-    </row>
-    <row r="137" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK136" s="1"/>
+      <c r="AL136" s="13"/>
+    </row>
+    <row r="137" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2">
@@ -10731,11 +11191,13 @@
       <c r="Q137" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R137" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T137" s="12"/>
-      <c r="U137" s="1"/>
+      <c r="R137" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U137" s="12"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
       <c r="X137" s="1"/>
@@ -10751,9 +11213,10 @@
       <c r="AH137" s="1"/>
       <c r="AI137" s="1"/>
       <c r="AJ137" s="1"/>
-      <c r="AK137" s="13"/>
-    </row>
-    <row r="138" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK137" s="1"/>
+      <c r="AL137" s="13"/>
+    </row>
+    <row r="138" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2">
@@ -10798,11 +11261,13 @@
       <c r="Q138" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R138" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T138" s="12"/>
-      <c r="U138" s="1"/>
+      <c r="R138" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U138" s="12"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
       <c r="X138" s="1"/>
@@ -10818,9 +11283,10 @@
       <c r="AH138" s="1"/>
       <c r="AI138" s="1"/>
       <c r="AJ138" s="1"/>
-      <c r="AK138" s="13"/>
-    </row>
-    <row r="139" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK138" s="1"/>
+      <c r="AL138" s="13"/>
+    </row>
+    <row r="139" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2">
@@ -10865,11 +11331,13 @@
       <c r="Q139" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R139" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T139" s="12"/>
-      <c r="U139" s="1"/>
+      <c r="R139" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U139" s="12"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
       <c r="X139" s="1"/>
@@ -10885,9 +11353,10 @@
       <c r="AH139" s="1"/>
       <c r="AI139" s="1"/>
       <c r="AJ139" s="1"/>
-      <c r="AK139" s="13"/>
-    </row>
-    <row r="140" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK139" s="1"/>
+      <c r="AL139" s="13"/>
+    </row>
+    <row r="140" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2">
@@ -10932,11 +11401,13 @@
       <c r="Q140" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R140" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T140" s="12"/>
-      <c r="U140" s="1"/>
+      <c r="R140" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U140" s="12"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
       <c r="X140" s="1"/>
@@ -10952,9 +11423,10 @@
       <c r="AH140" s="1"/>
       <c r="AI140" s="1"/>
       <c r="AJ140" s="1"/>
-      <c r="AK140" s="13"/>
-    </row>
-    <row r="141" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK140" s="1"/>
+      <c r="AL140" s="13"/>
+    </row>
+    <row r="141" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2">
@@ -10999,11 +11471,13 @@
       <c r="Q141" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R141" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T141" s="12"/>
-      <c r="U141" s="1"/>
+      <c r="R141" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U141" s="12"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
       <c r="X141" s="1"/>
@@ -11019,9 +11493,10 @@
       <c r="AH141" s="1"/>
       <c r="AI141" s="1"/>
       <c r="AJ141" s="1"/>
-      <c r="AK141" s="13"/>
-    </row>
-    <row r="142" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK141" s="1"/>
+      <c r="AL141" s="13"/>
+    </row>
+    <row r="142" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2">
@@ -11066,11 +11541,13 @@
       <c r="Q142" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R142" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T142" s="12"/>
-      <c r="U142" s="1"/>
+      <c r="R142" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U142" s="12"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
       <c r="X142" s="1"/>
@@ -11086,9 +11563,10 @@
       <c r="AH142" s="1"/>
       <c r="AI142" s="1"/>
       <c r="AJ142" s="1"/>
-      <c r="AK142" s="13"/>
-    </row>
-    <row r="143" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK142" s="1"/>
+      <c r="AL142" s="13"/>
+    </row>
+    <row r="143" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2">
@@ -11133,11 +11611,13 @@
       <c r="Q143" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R143" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T143" s="12"/>
-      <c r="U143" s="1"/>
+      <c r="R143" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U143" s="12"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
       <c r="X143" s="1"/>
@@ -11153,9 +11633,10 @@
       <c r="AH143" s="1"/>
       <c r="AI143" s="1"/>
       <c r="AJ143" s="1"/>
-      <c r="AK143" s="13"/>
-    </row>
-    <row r="144" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK143" s="1"/>
+      <c r="AL143" s="13"/>
+    </row>
+    <row r="144" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2">
@@ -11200,11 +11681,13 @@
       <c r="Q144" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R144" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T144" s="12"/>
-      <c r="U144" s="1"/>
+      <c r="R144" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U144" s="12"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
       <c r="X144" s="1"/>
@@ -11220,9 +11703,10 @@
       <c r="AH144" s="1"/>
       <c r="AI144" s="1"/>
       <c r="AJ144" s="1"/>
-      <c r="AK144" s="13"/>
-    </row>
-    <row r="145" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK144" s="1"/>
+      <c r="AL144" s="13"/>
+    </row>
+    <row r="145" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2">
@@ -11267,11 +11751,13 @@
       <c r="Q145" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R145" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T145" s="12"/>
-      <c r="U145" s="1"/>
+      <c r="R145" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S145" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U145" s="12"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
       <c r="X145" s="1"/>
@@ -11287,9 +11773,10 @@
       <c r="AH145" s="1"/>
       <c r="AI145" s="1"/>
       <c r="AJ145" s="1"/>
-      <c r="AK145" s="13"/>
-    </row>
-    <row r="146" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK145" s="1"/>
+      <c r="AL145" s="13"/>
+    </row>
+    <row r="146" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2">
@@ -11334,11 +11821,13 @@
       <c r="Q146" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R146" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T146" s="12"/>
-      <c r="U146" s="1"/>
+      <c r="R146" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U146" s="12"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
       <c r="X146" s="1"/>
@@ -11354,9 +11843,10 @@
       <c r="AH146" s="1"/>
       <c r="AI146" s="1"/>
       <c r="AJ146" s="1"/>
-      <c r="AK146" s="13"/>
-    </row>
-    <row r="147" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK146" s="1"/>
+      <c r="AL146" s="13"/>
+    </row>
+    <row r="147" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2">
@@ -11401,11 +11891,13 @@
       <c r="Q147" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R147" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T147" s="12"/>
-      <c r="U147" s="1"/>
+      <c r="R147" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U147" s="12"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
@@ -11421,9 +11913,10 @@
       <c r="AH147" s="1"/>
       <c r="AI147" s="1"/>
       <c r="AJ147" s="1"/>
-      <c r="AK147" s="13"/>
-    </row>
-    <row r="148" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK147" s="1"/>
+      <c r="AL147" s="13"/>
+    </row>
+    <row r="148" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2">
@@ -11468,11 +11961,13 @@
       <c r="Q148" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R148" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T148" s="12"/>
-      <c r="U148" s="1"/>
+      <c r="R148" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U148" s="12"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
       <c r="X148" s="1"/>
@@ -11488,9 +11983,10 @@
       <c r="AH148" s="1"/>
       <c r="AI148" s="1"/>
       <c r="AJ148" s="1"/>
-      <c r="AK148" s="13"/>
-    </row>
-    <row r="149" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK148" s="1"/>
+      <c r="AL148" s="13"/>
+    </row>
+    <row r="149" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2">
@@ -11535,11 +12031,13 @@
       <c r="Q149" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R149" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T149" s="12"/>
-      <c r="U149" s="1"/>
+      <c r="R149" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U149" s="12"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
       <c r="X149" s="1"/>
@@ -11555,9 +12053,10 @@
       <c r="AH149" s="1"/>
       <c r="AI149" s="1"/>
       <c r="AJ149" s="1"/>
-      <c r="AK149" s="13"/>
-    </row>
-    <row r="150" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK149" s="1"/>
+      <c r="AL149" s="13"/>
+    </row>
+    <row r="150" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2">
@@ -11602,11 +12101,13 @@
       <c r="Q150" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R150" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T150" s="12"/>
-      <c r="U150" s="1"/>
+      <c r="R150" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U150" s="12"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
       <c r="X150" s="1"/>
@@ -11622,9 +12123,10 @@
       <c r="AH150" s="1"/>
       <c r="AI150" s="1"/>
       <c r="AJ150" s="1"/>
-      <c r="AK150" s="13"/>
-    </row>
-    <row r="151" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK150" s="1"/>
+      <c r="AL150" s="13"/>
+    </row>
+    <row r="151" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2">
@@ -11669,11 +12171,13 @@
       <c r="Q151" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R151" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T151" s="12"/>
-      <c r="U151" s="1"/>
+      <c r="R151" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U151" s="12"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
       <c r="X151" s="1"/>
@@ -11689,9 +12193,10 @@
       <c r="AH151" s="1"/>
       <c r="AI151" s="1"/>
       <c r="AJ151" s="1"/>
-      <c r="AK151" s="13"/>
-    </row>
-    <row r="152" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK151" s="1"/>
+      <c r="AL151" s="13"/>
+    </row>
+    <row r="152" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2">
@@ -11736,11 +12241,13 @@
       <c r="Q152" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R152" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T152" s="12"/>
-      <c r="U152" s="1"/>
+      <c r="R152" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U152" s="12"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
       <c r="X152" s="1"/>
@@ -11756,9 +12263,10 @@
       <c r="AH152" s="1"/>
       <c r="AI152" s="1"/>
       <c r="AJ152" s="1"/>
-      <c r="AK152" s="13"/>
-    </row>
-    <row r="153" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK152" s="1"/>
+      <c r="AL152" s="13"/>
+    </row>
+    <row r="153" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2">
@@ -11803,11 +12311,13 @@
       <c r="Q153" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R153" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T153" s="12"/>
-      <c r="U153" s="1"/>
+      <c r="R153" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U153" s="12"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
       <c r="X153" s="1"/>
@@ -11823,9 +12333,10 @@
       <c r="AH153" s="1"/>
       <c r="AI153" s="1"/>
       <c r="AJ153" s="1"/>
-      <c r="AK153" s="13"/>
-    </row>
-    <row r="154" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK153" s="1"/>
+      <c r="AL153" s="13"/>
+    </row>
+    <row r="154" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2">
@@ -11870,11 +12381,13 @@
       <c r="Q154" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R154" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T154" s="12"/>
-      <c r="U154" s="1"/>
+      <c r="R154" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U154" s="12"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
       <c r="X154" s="1"/>
@@ -11890,9 +12403,10 @@
       <c r="AH154" s="1"/>
       <c r="AI154" s="1"/>
       <c r="AJ154" s="1"/>
-      <c r="AK154" s="13"/>
-    </row>
-    <row r="155" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK154" s="1"/>
+      <c r="AL154" s="13"/>
+    </row>
+    <row r="155" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2">
@@ -11937,11 +12451,13 @@
       <c r="Q155" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R155" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T155" s="12"/>
-      <c r="U155" s="1"/>
+      <c r="R155" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U155" s="12"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
       <c r="X155" s="1"/>
@@ -11957,9 +12473,10 @@
       <c r="AH155" s="1"/>
       <c r="AI155" s="1"/>
       <c r="AJ155" s="1"/>
-      <c r="AK155" s="13"/>
-    </row>
-    <row r="156" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK155" s="1"/>
+      <c r="AL155" s="13"/>
+    </row>
+    <row r="156" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2">
@@ -12004,11 +12521,13 @@
       <c r="Q156" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R156" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T156" s="12"/>
-      <c r="U156" s="1"/>
+      <c r="R156" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U156" s="12"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
       <c r="X156" s="1"/>
@@ -12024,9 +12543,10 @@
       <c r="AH156" s="1"/>
       <c r="AI156" s="1"/>
       <c r="AJ156" s="1"/>
-      <c r="AK156" s="13"/>
-    </row>
-    <row r="157" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK156" s="1"/>
+      <c r="AL156" s="13"/>
+    </row>
+    <row r="157" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2">
@@ -12071,11 +12591,13 @@
       <c r="Q157" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R157" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T157" s="12"/>
-      <c r="U157" s="1"/>
+      <c r="R157" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U157" s="12"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
       <c r="X157" s="1"/>
@@ -12091,9 +12613,10 @@
       <c r="AH157" s="1"/>
       <c r="AI157" s="1"/>
       <c r="AJ157" s="1"/>
-      <c r="AK157" s="13"/>
-    </row>
-    <row r="158" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK157" s="1"/>
+      <c r="AL157" s="13"/>
+    </row>
+    <row r="158" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2">
@@ -12138,11 +12661,13 @@
       <c r="Q158" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R158" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="T158" s="12"/>
-      <c r="U158" s="1"/>
+      <c r="R158" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U158" s="12"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
       <c r="X158" s="1"/>
@@ -12158,9 +12683,10 @@
       <c r="AH158" s="1"/>
       <c r="AI158" s="1"/>
       <c r="AJ158" s="1"/>
-      <c r="AK158" s="13"/>
-    </row>
-    <row r="159" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK158" s="1"/>
+      <c r="AL158" s="13"/>
+    </row>
+    <row r="159" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2">
@@ -12205,11 +12731,13 @@
       <c r="Q159" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R159" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T159" s="12"/>
-      <c r="U159" s="1"/>
+      <c r="R159" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S159" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U159" s="12"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
       <c r="X159" s="1"/>
@@ -12225,9 +12753,10 @@
       <c r="AH159" s="1"/>
       <c r="AI159" s="1"/>
       <c r="AJ159" s="1"/>
-      <c r="AK159" s="13"/>
-    </row>
-    <row r="160" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK159" s="1"/>
+      <c r="AL159" s="13"/>
+    </row>
+    <row r="160" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2">
@@ -12272,11 +12801,13 @@
       <c r="Q160" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R160" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T160" s="12"/>
-      <c r="U160" s="1"/>
+      <c r="R160" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S160" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U160" s="12"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
       <c r="X160" s="1"/>
@@ -12292,9 +12823,10 @@
       <c r="AH160" s="1"/>
       <c r="AI160" s="1"/>
       <c r="AJ160" s="1"/>
-      <c r="AK160" s="13"/>
-    </row>
-    <row r="161" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK160" s="1"/>
+      <c r="AL160" s="13"/>
+    </row>
+    <row r="161" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2">
@@ -12339,11 +12871,13 @@
       <c r="Q161" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R161" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T161" s="12"/>
-      <c r="U161" s="1"/>
+      <c r="R161" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S161" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U161" s="12"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
       <c r="X161" s="1"/>
@@ -12359,9 +12893,10 @@
       <c r="AH161" s="1"/>
       <c r="AI161" s="1"/>
       <c r="AJ161" s="1"/>
-      <c r="AK161" s="13"/>
-    </row>
-    <row r="162" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK161" s="1"/>
+      <c r="AL161" s="13"/>
+    </row>
+    <row r="162" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2">
@@ -12406,11 +12941,13 @@
       <c r="Q162" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R162" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T162" s="12"/>
-      <c r="U162" s="1"/>
+      <c r="R162" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S162" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U162" s="12"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
       <c r="X162" s="1"/>
@@ -12426,9 +12963,10 @@
       <c r="AH162" s="1"/>
       <c r="AI162" s="1"/>
       <c r="AJ162" s="1"/>
-      <c r="AK162" s="13"/>
-    </row>
-    <row r="163" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK162" s="1"/>
+      <c r="AL162" s="13"/>
+    </row>
+    <row r="163" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2">
@@ -12473,11 +13011,13 @@
       <c r="Q163" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R163" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T163" s="12"/>
-      <c r="U163" s="1"/>
+      <c r="R163" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S163" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U163" s="12"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
       <c r="X163" s="1"/>
@@ -12493,9 +13033,10 @@
       <c r="AH163" s="1"/>
       <c r="AI163" s="1"/>
       <c r="AJ163" s="1"/>
-      <c r="AK163" s="13"/>
-    </row>
-    <row r="164" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK163" s="1"/>
+      <c r="AL163" s="13"/>
+    </row>
+    <row r="164" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2">
@@ -12540,11 +13081,13 @@
       <c r="Q164" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R164" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T164" s="12"/>
-      <c r="U164" s="1"/>
+      <c r="R164" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S164" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U164" s="12"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
       <c r="X164" s="1"/>
@@ -12560,9 +13103,10 @@
       <c r="AH164" s="1"/>
       <c r="AI164" s="1"/>
       <c r="AJ164" s="1"/>
-      <c r="AK164" s="13"/>
-    </row>
-    <row r="165" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK164" s="1"/>
+      <c r="AL164" s="13"/>
+    </row>
+    <row r="165" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2">
@@ -12607,11 +13151,13 @@
       <c r="Q165" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R165" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T165" s="12"/>
-      <c r="U165" s="1"/>
+      <c r="R165" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S165" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U165" s="12"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
       <c r="X165" s="1"/>
@@ -12627,9 +13173,10 @@
       <c r="AH165" s="1"/>
       <c r="AI165" s="1"/>
       <c r="AJ165" s="1"/>
-      <c r="AK165" s="13"/>
-    </row>
-    <row r="166" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK165" s="1"/>
+      <c r="AL165" s="13"/>
+    </row>
+    <row r="166" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2">
@@ -12674,11 +13221,13 @@
       <c r="Q166" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R166" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T166" s="12"/>
-      <c r="U166" s="1"/>
+      <c r="R166" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S166" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U166" s="12"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
       <c r="X166" s="1"/>
@@ -12694,9 +13243,10 @@
       <c r="AH166" s="1"/>
       <c r="AI166" s="1"/>
       <c r="AJ166" s="1"/>
-      <c r="AK166" s="13"/>
-    </row>
-    <row r="167" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK166" s="1"/>
+      <c r="AL166" s="13"/>
+    </row>
+    <row r="167" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2">
@@ -12741,11 +13291,13 @@
       <c r="Q167" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R167" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T167" s="12"/>
-      <c r="U167" s="1"/>
+      <c r="R167" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S167" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U167" s="12"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
       <c r="X167" s="1"/>
@@ -12761,9 +13313,10 @@
       <c r="AH167" s="1"/>
       <c r="AI167" s="1"/>
       <c r="AJ167" s="1"/>
-      <c r="AK167" s="13"/>
-    </row>
-    <row r="168" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK167" s="1"/>
+      <c r="AL167" s="13"/>
+    </row>
+    <row r="168" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2">
@@ -12808,11 +13361,13 @@
       <c r="Q168" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R168" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T168" s="12"/>
-      <c r="U168" s="1"/>
+      <c r="R168" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S168" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U168" s="12"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
       <c r="X168" s="1"/>
@@ -12828,9 +13383,10 @@
       <c r="AH168" s="1"/>
       <c r="AI168" s="1"/>
       <c r="AJ168" s="1"/>
-      <c r="AK168" s="13"/>
-    </row>
-    <row r="169" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK168" s="1"/>
+      <c r="AL168" s="13"/>
+    </row>
+    <row r="169" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2">
@@ -12875,11 +13431,13 @@
       <c r="Q169" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R169" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T169" s="12"/>
-      <c r="U169" s="1"/>
+      <c r="R169" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S169" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U169" s="12"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
       <c r="X169" s="1"/>
@@ -12895,9 +13453,10 @@
       <c r="AH169" s="1"/>
       <c r="AI169" s="1"/>
       <c r="AJ169" s="1"/>
-      <c r="AK169" s="13"/>
-    </row>
-    <row r="170" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK169" s="1"/>
+      <c r="AL169" s="13"/>
+    </row>
+    <row r="170" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2">
@@ -12942,11 +13501,13 @@
       <c r="Q170" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R170" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T170" s="12"/>
-      <c r="U170" s="1"/>
+      <c r="R170" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S170" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U170" s="12"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
       <c r="X170" s="1"/>
@@ -12962,9 +13523,10 @@
       <c r="AH170" s="1"/>
       <c r="AI170" s="1"/>
       <c r="AJ170" s="1"/>
-      <c r="AK170" s="13"/>
-    </row>
-    <row r="171" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK170" s="1"/>
+      <c r="AL170" s="13"/>
+    </row>
+    <row r="171" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2">
@@ -13009,11 +13571,13 @@
       <c r="Q171" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R171" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T171" s="12"/>
-      <c r="U171" s="1"/>
+      <c r="R171" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S171" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U171" s="12"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
       <c r="X171" s="1"/>
@@ -13029,9 +13593,10 @@
       <c r="AH171" s="1"/>
       <c r="AI171" s="1"/>
       <c r="AJ171" s="1"/>
-      <c r="AK171" s="13"/>
-    </row>
-    <row r="172" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK171" s="1"/>
+      <c r="AL171" s="13"/>
+    </row>
+    <row r="172" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2">
@@ -13076,11 +13641,13 @@
       <c r="Q172" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R172" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T172" s="12"/>
-      <c r="U172" s="1"/>
+      <c r="R172" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S172" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U172" s="12"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
       <c r="X172" s="1"/>
@@ -13096,9 +13663,10 @@
       <c r="AH172" s="1"/>
       <c r="AI172" s="1"/>
       <c r="AJ172" s="1"/>
-      <c r="AK172" s="13"/>
-    </row>
-    <row r="173" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK172" s="1"/>
+      <c r="AL172" s="13"/>
+    </row>
+    <row r="173" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2">
@@ -13143,11 +13711,13 @@
       <c r="Q173" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R173" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T173" s="12"/>
-      <c r="U173" s="1"/>
+      <c r="R173" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S173" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U173" s="12"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
       <c r="X173" s="1"/>
@@ -13163,9 +13733,10 @@
       <c r="AH173" s="1"/>
       <c r="AI173" s="1"/>
       <c r="AJ173" s="1"/>
-      <c r="AK173" s="13"/>
-    </row>
-    <row r="174" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK173" s="1"/>
+      <c r="AL173" s="13"/>
+    </row>
+    <row r="174" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2">
@@ -13210,11 +13781,13 @@
       <c r="Q174" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R174" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T174" s="12"/>
-      <c r="U174" s="1"/>
+      <c r="R174" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S174" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U174" s="12"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
@@ -13230,9 +13803,10 @@
       <c r="AH174" s="1"/>
       <c r="AI174" s="1"/>
       <c r="AJ174" s="1"/>
-      <c r="AK174" s="13"/>
-    </row>
-    <row r="175" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK174" s="1"/>
+      <c r="AL174" s="13"/>
+    </row>
+    <row r="175" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2">
@@ -13277,11 +13851,13 @@
       <c r="Q175" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R175" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T175" s="12"/>
-      <c r="U175" s="1"/>
+      <c r="R175" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S175" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U175" s="12"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
       <c r="X175" s="1"/>
@@ -13297,9 +13873,10 @@
       <c r="AH175" s="1"/>
       <c r="AI175" s="1"/>
       <c r="AJ175" s="1"/>
-      <c r="AK175" s="13"/>
-    </row>
-    <row r="176" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK175" s="1"/>
+      <c r="AL175" s="13"/>
+    </row>
+    <row r="176" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2">
@@ -13344,11 +13921,13 @@
       <c r="Q176" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R176" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T176" s="12"/>
-      <c r="U176" s="1"/>
+      <c r="R176" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S176" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U176" s="12"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
       <c r="X176" s="1"/>
@@ -13364,9 +13943,10 @@
       <c r="AH176" s="1"/>
       <c r="AI176" s="1"/>
       <c r="AJ176" s="1"/>
-      <c r="AK176" s="13"/>
-    </row>
-    <row r="177" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK176" s="1"/>
+      <c r="AL176" s="13"/>
+    </row>
+    <row r="177" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2">
@@ -13411,11 +13991,13 @@
       <c r="Q177" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R177" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T177" s="12"/>
-      <c r="U177" s="1"/>
+      <c r="R177" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S177" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U177" s="12"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
       <c r="X177" s="1"/>
@@ -13431,9 +14013,10 @@
       <c r="AH177" s="1"/>
       <c r="AI177" s="1"/>
       <c r="AJ177" s="1"/>
-      <c r="AK177" s="13"/>
-    </row>
-    <row r="178" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK177" s="1"/>
+      <c r="AL177" s="13"/>
+    </row>
+    <row r="178" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2">
@@ -13478,11 +14061,13 @@
       <c r="Q178" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R178" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T178" s="12"/>
-      <c r="U178" s="1"/>
+      <c r="R178" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S178" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U178" s="12"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
       <c r="X178" s="1"/>
@@ -13498,9 +14083,10 @@
       <c r="AH178" s="1"/>
       <c r="AI178" s="1"/>
       <c r="AJ178" s="1"/>
-      <c r="AK178" s="13"/>
-    </row>
-    <row r="179" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK178" s="1"/>
+      <c r="AL178" s="13"/>
+    </row>
+    <row r="179" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2">
@@ -13545,11 +14131,13 @@
       <c r="Q179" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R179" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T179" s="12"/>
-      <c r="U179" s="1"/>
+      <c r="R179" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="S179" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U179" s="12"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
       <c r="X179" s="1"/>
@@ -13565,9 +14153,10 @@
       <c r="AH179" s="1"/>
       <c r="AI179" s="1"/>
       <c r="AJ179" s="1"/>
-      <c r="AK179" s="13"/>
-    </row>
-    <row r="180" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AK179" s="1"/>
+      <c r="AL179" s="13"/>
+    </row>
+    <row r="180" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="8"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9">
@@ -13612,11 +14201,13 @@
       <c r="Q180" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="R180" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="T180" s="14"/>
-      <c r="U180" s="15"/>
+      <c r="R180" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="S180" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="U180" s="14"/>
       <c r="V180" s="15"/>
       <c r="W180" s="15"/>
       <c r="X180" s="15"/>
@@ -13632,14 +14223,37 @@
       <c r="AH180" s="15"/>
       <c r="AI180" s="15"/>
       <c r="AJ180" s="15"/>
-      <c r="AK180" s="16"/>
+      <c r="AK180" s="15"/>
+      <c r="AL180" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AG2:AG4"/>
+    <mergeCell ref="AH2:AH4"/>
+    <mergeCell ref="AI2:AI4"/>
+    <mergeCell ref="AJ2:AJ4"/>
+    <mergeCell ref="U2:U4"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="U1:AL1"/>
+    <mergeCell ref="AK2:AK4"/>
+    <mergeCell ref="AL2:AL4"/>
+    <mergeCell ref="W2:W4"/>
+    <mergeCell ref="X2:X4"/>
+    <mergeCell ref="Y2:Y4"/>
+    <mergeCell ref="Z2:Z4"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="AB2:AB4"/>
+    <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="AD2:AD4"/>
+    <mergeCell ref="AE2:AE4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="S2:S4"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -13652,27 +14266,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="T2:T4"/>
-    <mergeCell ref="U2:U4"/>
-    <mergeCell ref="P2:P4"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="T1:AK1"/>
-    <mergeCell ref="AJ2:AJ4"/>
-    <mergeCell ref="AK2:AK4"/>
-    <mergeCell ref="V2:V4"/>
-    <mergeCell ref="W2:W4"/>
-    <mergeCell ref="X2:X4"/>
-    <mergeCell ref="Y2:Y4"/>
-    <mergeCell ref="Z2:Z4"/>
-    <mergeCell ref="AA2:AA4"/>
-    <mergeCell ref="AB2:AB4"/>
-    <mergeCell ref="AC2:AC4"/>
-    <mergeCell ref="AD2:AD4"/>
-    <mergeCell ref="AE2:AE4"/>
-    <mergeCell ref="AF2:AF4"/>
-    <mergeCell ref="AG2:AG4"/>
-    <mergeCell ref="AH2:AH4"/>
-    <mergeCell ref="AI2:AI4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DATA/DATA FILES/VFD DATA.xlsx
+++ b/DATA/DATA FILES/VFD DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HHpro\DATA\DATA FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB40DAB6-F3F9-4ED8-B930-5E86BEB569DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591B0466-DAF5-45B3-8FE2-E34510E78C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CF7C304B-F6B4-4B1F-B338-76877CE5AAA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{CF7C304B-F6B4-4B1F-B338-76877CE5AAA5}"/>
   </bookViews>
   <sheets>
     <sheet name="SCHEDULE" sheetId="1" r:id="rId1"/>
@@ -660,54 +660,6 @@
     <t>1, 2, 3, 4, 5, 6, 13, 14, 15, 16</t>
   </si>
   <si>
-    <t>1. At minimum, VFD shall include 5% impedance via 5% AC line reactor or dual DC bus chokes sized to 5% equivalent impedance.  VFD input Amps shall not exceed VFD output Amps.</t>
-  </si>
-  <si>
-    <t>2. Provide UL1449 surge suppression device.</t>
-  </si>
-  <si>
-    <t>3. VFD shall include alpha-numeric keypad interface, with display in plain English.  (Displays relying solely on codes are not acceptable).</t>
-  </si>
-  <si>
-    <t>4. Provide internal EMI/RFI filter per IEC 61800-3.</t>
-  </si>
-  <si>
-    <t>5. VFD shall be BTL Listed for BACnet MS/TP, and also include Modbus and N2.</t>
-  </si>
-  <si>
-    <t>6. VFD shall include real time clock with battery backup (include 10 year battery).</t>
-  </si>
-  <si>
-    <t>7. Phase Loss Protection &amp; Broken Belt (loss of load) indication while in Bypass.</t>
-  </si>
-  <si>
-    <t>8. Bypass Contactors shall be powered by Switch Mode Power supply, allowing +30% to -30% Input Voltage Tolerance.  (120 V CPT not allowed).</t>
-  </si>
-  <si>
-    <t>9. VFD and Bypass shall both include BACnet MS/TP, Damper Control and Fireman’s override functionality.</t>
-  </si>
-  <si>
-    <t>10. Bypass operation to auto-reset after a brown out condition.</t>
-  </si>
-  <si>
-    <t>11. Include fast acting drive isolation fuses.</t>
-  </si>
-  <si>
-    <t>12. Bypass shall be fully functional in the event of a VFD failure.  Bypass shall not relay on the VFD or the VFD’s control board/relays.</t>
-  </si>
-  <si>
-    <t>13. Passive harmonic filter shall be factory mounted in the same enclosure as the VFD.</t>
-  </si>
-  <si>
-    <t>14. Passive harmonic filter shall include capacitor drop-out contactor.</t>
-  </si>
-  <si>
-    <t>15. Passive harmonic filter shall reduce harmonics to 5% THiD, measured at the filter lugs, while operating at full load.</t>
-  </si>
-  <si>
-    <t>16. System to meet IEEE 519-2014 based on the harmonic mitigation method(s) identified in the above schedule</t>
-  </si>
-  <si>
     <t>SCHEDULE RANGE</t>
   </si>
   <si>
@@ -787,6 +739,54 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>At minimum, VFD shall include 5% impedance via 5% AC line reactor or dual DC bus chokes sized to 5% equivalent impedance.  VFD input Amps shall not exceed VFD output Amps.</t>
+  </si>
+  <si>
+    <t>Provide UL1449 surge suppression device.</t>
+  </si>
+  <si>
+    <t>VFD shall include alpha-numeric keypad interface, with display in plain English.  (Displays relying solely on codes are not acceptable).</t>
+  </si>
+  <si>
+    <t>Provide internal EMI/RFI filter per IEC 61800-3.</t>
+  </si>
+  <si>
+    <t>VFD shall be BTL Listed for BACnet MS/TP, and also include Modbus and N2.</t>
+  </si>
+  <si>
+    <t>VFD shall include real time clock with battery backup (include 10 year battery).</t>
+  </si>
+  <si>
+    <t>Phase Loss Protection &amp; Broken Belt (loss of load) indication while in Bypass.</t>
+  </si>
+  <si>
+    <t>Bypass Contactors shall be powered by Switch Mode Power supply, allowing +30% to -30% Input Voltage Tolerance.  (120 V CPT not allowed).</t>
+  </si>
+  <si>
+    <t>VFD and Bypass shall both include BACnet MS/TP, Damper Control and Fireman’s override functionality.</t>
+  </si>
+  <si>
+    <t>Bypass operation to auto-reset after a brown out condition.</t>
+  </si>
+  <si>
+    <t>Include fast acting drive isolation fuses.</t>
+  </si>
+  <si>
+    <t>Bypass shall be fully functional in the event of a VFD failure.  Bypass shall not relay on the VFD or the VFD’s control board/relays.</t>
+  </si>
+  <si>
+    <t>Passive harmonic filter shall be factory mounted in the same enclosure as the VFD.</t>
+  </si>
+  <si>
+    <t>Passive harmonic filter shall include capacitor drop-out contactor.</t>
+  </si>
+  <si>
+    <t>Passive harmonic filter shall reduce harmonics to 5% THiD, measured at the filter lugs, while operating at full load.</t>
+  </si>
+  <si>
+    <t>System to meet IEEE 519-2014 based on the harmonic mitigation method(s) identified in the above schedule</t>
   </si>
 </sst>
 </file>
@@ -1236,6 +1236,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1245,10 +1263,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1280,27 +1301,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1673,169 +1673,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="28"/>
+      <c r="O1" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="28"/>
+      <c r="U1" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="30"/>
+      <c r="AI1" s="30"/>
+      <c r="AJ1" s="30"/>
+      <c r="AK1" s="30"/>
+      <c r="AL1" s="31"/>
+    </row>
+    <row r="2" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="34"/>
+      <c r="O2" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="P2" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q2" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="R2" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="S2" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="U2" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="V2" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="X2" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y2" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z2" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA2" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB2" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="AC2" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD2" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="22"/>
-      <c r="O1" s="20" t="s">
+      <c r="AE2" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="22"/>
-      <c r="U1" s="35" t="s">
+      <c r="AF2" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="AG2" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="AH2" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="AI2" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="36"/>
-      <c r="AL1" s="37"/>
-    </row>
-    <row r="2" spans="1:38" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27"/>
-      <c r="O2" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="P2" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="R2" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="S2" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="U2" s="23" t="s">
+      <c r="AK2" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="AL2" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="W2" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="X2" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y2" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="Z2" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA2" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="AB2" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC2" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="AD2" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="AE2" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="AF2" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="AG2" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="AH2" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="AI2" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="AJ2" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="AK2" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="AL2" s="23" t="s">
-        <v>246</v>
-      </c>
     </row>
     <row r="3" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="28" t="s">
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="28" t="s">
+      <c r="L3" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="28" t="s">
+      <c r="M3" s="35" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="24"/>
@@ -1863,8 +1863,8 @@
       <c r="AL3" s="24"/>
     </row>
     <row r="4" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="11" t="s">
         <v>12</v>
       </c>
@@ -1874,18 +1874,18 @@
       <c r="E4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
       <c r="S4" s="24"/>
       <c r="U4" s="24"/>
       <c r="V4" s="24"/>
@@ -1951,7 +1951,7 @@
       <c r="Q5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="38" t="s">
+      <c r="R5" s="20" t="s">
         <v>19</v>
       </c>
       <c r="S5" s="5" t="s">
@@ -2021,7 +2021,7 @@
       <c r="Q6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="39" t="s">
+      <c r="R6" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S6" s="7" t="s">
@@ -2091,7 +2091,7 @@
       <c r="Q7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R7" s="39" t="s">
+      <c r="R7" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S7" s="7" t="s">
@@ -2161,7 +2161,7 @@
       <c r="Q8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R8" s="39" t="s">
+      <c r="R8" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S8" s="7" t="s">
@@ -2231,7 +2231,7 @@
       <c r="Q9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R9" s="39" t="s">
+      <c r="R9" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S9" s="7" t="s">
@@ -2301,7 +2301,7 @@
       <c r="Q10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R10" s="39" t="s">
+      <c r="R10" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S10" s="7" t="s">
@@ -2371,7 +2371,7 @@
       <c r="Q11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="39" t="s">
+      <c r="R11" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S11" s="7" t="s">
@@ -2441,7 +2441,7 @@
       <c r="Q12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R12" s="39" t="s">
+      <c r="R12" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S12" s="7" t="s">
@@ -2511,7 +2511,7 @@
       <c r="Q13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R13" s="39" t="s">
+      <c r="R13" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S13" s="7" t="s">
@@ -2581,7 +2581,7 @@
       <c r="Q14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="39" t="s">
+      <c r="R14" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S14" s="7" t="s">
@@ -2651,7 +2651,7 @@
       <c r="Q15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="39" t="s">
+      <c r="R15" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S15" s="7" t="s">
@@ -2721,7 +2721,7 @@
       <c r="Q16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R16" s="39" t="s">
+      <c r="R16" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S16" s="7" t="s">
@@ -2791,7 +2791,7 @@
       <c r="Q17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="39" t="s">
+      <c r="R17" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S17" s="7" t="s">
@@ -2861,7 +2861,7 @@
       <c r="Q18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R18" s="39" t="s">
+      <c r="R18" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S18" s="7" t="s">
@@ -2931,7 +2931,7 @@
       <c r="Q19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R19" s="39" t="s">
+      <c r="R19" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S19" s="7" t="s">
@@ -3001,7 +3001,7 @@
       <c r="Q20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="39" t="s">
+      <c r="R20" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S20" s="7" t="s">
@@ -3071,7 +3071,7 @@
       <c r="Q21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R21" s="39" t="s">
+      <c r="R21" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S21" s="7" t="s">
@@ -3141,7 +3141,7 @@
       <c r="Q22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="39" t="s">
+      <c r="R22" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S22" s="7" t="s">
@@ -3211,7 +3211,7 @@
       <c r="Q23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R23" s="39" t="s">
+      <c r="R23" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S23" s="7" t="s">
@@ -3281,7 +3281,7 @@
       <c r="Q24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R24" s="39" t="s">
+      <c r="R24" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S24" s="7" t="s">
@@ -3351,7 +3351,7 @@
       <c r="Q25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R25" s="39" t="s">
+      <c r="R25" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S25" s="7" t="s">
@@ -3421,7 +3421,7 @@
       <c r="Q26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R26" s="39" t="s">
+      <c r="R26" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S26" s="7" t="s">
@@ -3491,7 +3491,7 @@
       <c r="Q27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="39" t="s">
+      <c r="R27" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S27" s="7" t="s">
@@ -3561,7 +3561,7 @@
       <c r="Q28" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R28" s="39" t="s">
+      <c r="R28" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S28" s="7" t="s">
@@ -3631,7 +3631,7 @@
       <c r="Q29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="39" t="s">
+      <c r="R29" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S29" s="7" t="s">
@@ -3701,7 +3701,7 @@
       <c r="Q30" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R30" s="39" t="s">
+      <c r="R30" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S30" s="7" t="s">
@@ -3771,7 +3771,7 @@
       <c r="Q31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R31" s="39" t="s">
+      <c r="R31" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S31" s="7" t="s">
@@ -3841,7 +3841,7 @@
       <c r="Q32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R32" s="39" t="s">
+      <c r="R32" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S32" s="7" t="s">
@@ -3911,7 +3911,7 @@
       <c r="Q33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R33" s="39" t="s">
+      <c r="R33" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S33" s="7" t="s">
@@ -3981,7 +3981,7 @@
       <c r="Q34" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R34" s="39" t="s">
+      <c r="R34" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S34" s="7" t="s">
@@ -4051,7 +4051,7 @@
       <c r="Q35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R35" s="39" t="s">
+      <c r="R35" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S35" s="7" t="s">
@@ -4121,7 +4121,7 @@
       <c r="Q36" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R36" s="39" t="s">
+      <c r="R36" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S36" s="7" t="s">
@@ -4191,7 +4191,7 @@
       <c r="Q37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R37" s="39" t="s">
+      <c r="R37" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S37" s="7" t="s">
@@ -4261,7 +4261,7 @@
       <c r="Q38" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R38" s="39" t="s">
+      <c r="R38" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S38" s="7" t="s">
@@ -4331,7 +4331,7 @@
       <c r="Q39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R39" s="39" t="s">
+      <c r="R39" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S39" s="7" t="s">
@@ -4401,7 +4401,7 @@
       <c r="Q40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R40" s="39" t="s">
+      <c r="R40" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S40" s="7" t="s">
@@ -4471,7 +4471,7 @@
       <c r="Q41" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R41" s="39" t="s">
+      <c r="R41" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S41" s="7" t="s">
@@ -4541,7 +4541,7 @@
       <c r="Q42" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R42" s="39" t="s">
+      <c r="R42" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S42" s="7" t="s">
@@ -4611,7 +4611,7 @@
       <c r="Q43" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R43" s="39" t="s">
+      <c r="R43" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S43" s="7" t="s">
@@ -4681,7 +4681,7 @@
       <c r="Q44" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R44" s="39" t="s">
+      <c r="R44" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S44" s="7" t="s">
@@ -4751,7 +4751,7 @@
       <c r="Q45" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R45" s="39" t="s">
+      <c r="R45" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S45" s="7" t="s">
@@ -4821,7 +4821,7 @@
       <c r="Q46" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R46" s="39" t="s">
+      <c r="R46" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S46" s="7" t="s">
@@ -4891,7 +4891,7 @@
       <c r="Q47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R47" s="39" t="s">
+      <c r="R47" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S47" s="7" t="s">
@@ -4961,7 +4961,7 @@
       <c r="Q48" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R48" s="39" t="s">
+      <c r="R48" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S48" s="7" t="s">
@@ -5031,7 +5031,7 @@
       <c r="Q49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R49" s="39" t="s">
+      <c r="R49" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S49" s="7" t="s">
@@ -5101,7 +5101,7 @@
       <c r="Q50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R50" s="39" t="s">
+      <c r="R50" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S50" s="7" t="s">
@@ -5171,7 +5171,7 @@
       <c r="Q51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R51" s="39" t="s">
+      <c r="R51" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S51" s="7" t="s">
@@ -5241,7 +5241,7 @@
       <c r="Q52" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R52" s="39" t="s">
+      <c r="R52" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S52" s="7" t="s">
@@ -5311,7 +5311,7 @@
       <c r="Q53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R53" s="39" t="s">
+      <c r="R53" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S53" s="7" t="s">
@@ -5381,7 +5381,7 @@
       <c r="Q54" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R54" s="39" t="s">
+      <c r="R54" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S54" s="7" t="s">
@@ -5451,7 +5451,7 @@
       <c r="Q55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R55" s="39" t="s">
+      <c r="R55" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S55" s="7" t="s">
@@ -5521,7 +5521,7 @@
       <c r="Q56" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R56" s="39" t="s">
+      <c r="R56" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S56" s="7" t="s">
@@ -5591,7 +5591,7 @@
       <c r="Q57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R57" s="39" t="s">
+      <c r="R57" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S57" s="7" t="s">
@@ -5661,7 +5661,7 @@
       <c r="Q58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R58" s="39" t="s">
+      <c r="R58" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S58" s="7" t="s">
@@ -5731,7 +5731,7 @@
       <c r="Q59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R59" s="39" t="s">
+      <c r="R59" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S59" s="7" t="s">
@@ -5801,7 +5801,7 @@
       <c r="Q60" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R60" s="39" t="s">
+      <c r="R60" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S60" s="7" t="s">
@@ -5871,7 +5871,7 @@
       <c r="Q61" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R61" s="39" t="s">
+      <c r="R61" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S61" s="7" t="s">
@@ -5941,7 +5941,7 @@
       <c r="Q62" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R62" s="39" t="s">
+      <c r="R62" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S62" s="7" t="s">
@@ -6011,7 +6011,7 @@
       <c r="Q63" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R63" s="39" t="s">
+      <c r="R63" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S63" s="7" t="s">
@@ -6081,7 +6081,7 @@
       <c r="Q64" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R64" s="39" t="s">
+      <c r="R64" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S64" s="7" t="s">
@@ -6151,7 +6151,7 @@
       <c r="Q65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R65" s="39" t="s">
+      <c r="R65" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S65" s="7" t="s">
@@ -6221,7 +6221,7 @@
       <c r="Q66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R66" s="39" t="s">
+      <c r="R66" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S66" s="7" t="s">
@@ -6291,7 +6291,7 @@
       <c r="Q67" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R67" s="39" t="s">
+      <c r="R67" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S67" s="7" t="s">
@@ -6361,7 +6361,7 @@
       <c r="Q68" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R68" s="39" t="s">
+      <c r="R68" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S68" s="7" t="s">
@@ -6431,7 +6431,7 @@
       <c r="Q69" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R69" s="39" t="s">
+      <c r="R69" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S69" s="7" t="s">
@@ -6501,7 +6501,7 @@
       <c r="Q70" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R70" s="39" t="s">
+      <c r="R70" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S70" s="7" t="s">
@@ -6571,7 +6571,7 @@
       <c r="Q71" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R71" s="39" t="s">
+      <c r="R71" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S71" s="7" t="s">
@@ -6641,7 +6641,7 @@
       <c r="Q72" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R72" s="39" t="s">
+      <c r="R72" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S72" s="7" t="s">
@@ -6711,7 +6711,7 @@
       <c r="Q73" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R73" s="39" t="s">
+      <c r="R73" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S73" s="7" t="s">
@@ -6781,7 +6781,7 @@
       <c r="Q74" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R74" s="39" t="s">
+      <c r="R74" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S74" s="7" t="s">
@@ -6851,7 +6851,7 @@
       <c r="Q75" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R75" s="39" t="s">
+      <c r="R75" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S75" s="7" t="s">
@@ -6921,7 +6921,7 @@
       <c r="Q76" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R76" s="39" t="s">
+      <c r="R76" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S76" s="7" t="s">
@@ -6991,7 +6991,7 @@
       <c r="Q77" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R77" s="39" t="s">
+      <c r="R77" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S77" s="7" t="s">
@@ -7061,7 +7061,7 @@
       <c r="Q78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R78" s="39" t="s">
+      <c r="R78" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S78" s="7" t="s">
@@ -7131,7 +7131,7 @@
       <c r="Q79" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R79" s="39" t="s">
+      <c r="R79" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S79" s="7" t="s">
@@ -7201,7 +7201,7 @@
       <c r="Q80" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R80" s="39" t="s">
+      <c r="R80" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S80" s="7" t="s">
@@ -7271,7 +7271,7 @@
       <c r="Q81" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R81" s="39" t="s">
+      <c r="R81" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S81" s="7" t="s">
@@ -7341,7 +7341,7 @@
       <c r="Q82" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R82" s="39" t="s">
+      <c r="R82" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S82" s="7" t="s">
@@ -7411,7 +7411,7 @@
       <c r="Q83" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R83" s="39" t="s">
+      <c r="R83" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S83" s="7" t="s">
@@ -7481,7 +7481,7 @@
       <c r="Q84" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R84" s="39" t="s">
+      <c r="R84" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S84" s="7" t="s">
@@ -7551,7 +7551,7 @@
       <c r="Q85" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R85" s="39" t="s">
+      <c r="R85" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S85" s="7" t="s">
@@ -7621,7 +7621,7 @@
       <c r="Q86" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R86" s="39" t="s">
+      <c r="R86" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S86" s="7" t="s">
@@ -7691,7 +7691,7 @@
       <c r="Q87" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R87" s="39" t="s">
+      <c r="R87" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S87" s="7" t="s">
@@ -7761,7 +7761,7 @@
       <c r="Q88" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R88" s="39" t="s">
+      <c r="R88" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S88" s="7" t="s">
@@ -7831,7 +7831,7 @@
       <c r="Q89" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R89" s="39" t="s">
+      <c r="R89" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S89" s="7" t="s">
@@ -7901,7 +7901,7 @@
       <c r="Q90" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R90" s="39" t="s">
+      <c r="R90" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S90" s="7" t="s">
@@ -7971,7 +7971,7 @@
       <c r="Q91" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R91" s="39" t="s">
+      <c r="R91" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S91" s="7" t="s">
@@ -8041,7 +8041,7 @@
       <c r="Q92" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R92" s="39" t="s">
+      <c r="R92" s="21" t="s">
         <v>19</v>
       </c>
       <c r="S92" s="7" t="s">
@@ -8111,8 +8111,8 @@
       <c r="Q93" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R93" s="39" t="s">
-        <v>248</v>
+      <c r="R93" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S93" s="7" t="s">
         <v>17</v>
@@ -8181,8 +8181,8 @@
       <c r="Q94" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R94" s="39" t="s">
-        <v>248</v>
+      <c r="R94" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S94" s="7" t="s">
         <v>17</v>
@@ -8251,8 +8251,8 @@
       <c r="Q95" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R95" s="39" t="s">
-        <v>248</v>
+      <c r="R95" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S95" s="7" t="s">
         <v>17</v>
@@ -8321,8 +8321,8 @@
       <c r="Q96" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R96" s="39" t="s">
-        <v>248</v>
+      <c r="R96" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S96" s="7" t="s">
         <v>17</v>
@@ -8391,8 +8391,8 @@
       <c r="Q97" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R97" s="39" t="s">
-        <v>248</v>
+      <c r="R97" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S97" s="7" t="s">
         <v>17</v>
@@ -8461,8 +8461,8 @@
       <c r="Q98" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R98" s="39" t="s">
-        <v>248</v>
+      <c r="R98" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S98" s="7" t="s">
         <v>17</v>
@@ -8531,8 +8531,8 @@
       <c r="Q99" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R99" s="39" t="s">
-        <v>248</v>
+      <c r="R99" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S99" s="7" t="s">
         <v>17</v>
@@ -8601,8 +8601,8 @@
       <c r="Q100" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R100" s="39" t="s">
-        <v>248</v>
+      <c r="R100" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S100" s="7" t="s">
         <v>17</v>
@@ -8671,8 +8671,8 @@
       <c r="Q101" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R101" s="39" t="s">
-        <v>248</v>
+      <c r="R101" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S101" s="7" t="s">
         <v>17</v>
@@ -8741,8 +8741,8 @@
       <c r="Q102" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R102" s="39" t="s">
-        <v>248</v>
+      <c r="R102" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S102" s="7" t="s">
         <v>17</v>
@@ -8811,8 +8811,8 @@
       <c r="Q103" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R103" s="39" t="s">
-        <v>248</v>
+      <c r="R103" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S103" s="7" t="s">
         <v>17</v>
@@ -8881,8 +8881,8 @@
       <c r="Q104" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R104" s="39" t="s">
-        <v>248</v>
+      <c r="R104" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S104" s="7" t="s">
         <v>17</v>
@@ -8951,8 +8951,8 @@
       <c r="Q105" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R105" s="39" t="s">
-        <v>248</v>
+      <c r="R105" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S105" s="7" t="s">
         <v>17</v>
@@ -9021,8 +9021,8 @@
       <c r="Q106" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R106" s="39" t="s">
-        <v>248</v>
+      <c r="R106" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S106" s="7" t="s">
         <v>17</v>
@@ -9091,8 +9091,8 @@
       <c r="Q107" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R107" s="39" t="s">
-        <v>248</v>
+      <c r="R107" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S107" s="7" t="s">
         <v>17</v>
@@ -9161,8 +9161,8 @@
       <c r="Q108" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R108" s="39" t="s">
-        <v>248</v>
+      <c r="R108" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S108" s="7" t="s">
         <v>17</v>
@@ -9231,8 +9231,8 @@
       <c r="Q109" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R109" s="39" t="s">
-        <v>248</v>
+      <c r="R109" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S109" s="7" t="s">
         <v>17</v>
@@ -9301,8 +9301,8 @@
       <c r="Q110" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R110" s="39" t="s">
-        <v>248</v>
+      <c r="R110" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S110" s="7" t="s">
         <v>17</v>
@@ -9371,8 +9371,8 @@
       <c r="Q111" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R111" s="39" t="s">
-        <v>248</v>
+      <c r="R111" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S111" s="7" t="s">
         <v>17</v>
@@ -9441,8 +9441,8 @@
       <c r="Q112" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R112" s="39" t="s">
-        <v>248</v>
+      <c r="R112" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S112" s="7" t="s">
         <v>17</v>
@@ -9511,8 +9511,8 @@
       <c r="Q113" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R113" s="39" t="s">
-        <v>248</v>
+      <c r="R113" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S113" s="7" t="s">
         <v>17</v>
@@ -9581,8 +9581,8 @@
       <c r="Q114" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R114" s="39" t="s">
-        <v>248</v>
+      <c r="R114" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S114" s="7" t="s">
         <v>17</v>
@@ -9651,8 +9651,8 @@
       <c r="Q115" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R115" s="39" t="s">
-        <v>248</v>
+      <c r="R115" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S115" s="7" t="s">
         <v>22</v>
@@ -9721,8 +9721,8 @@
       <c r="Q116" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R116" s="39" t="s">
-        <v>248</v>
+      <c r="R116" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S116" s="7" t="s">
         <v>22</v>
@@ -9791,8 +9791,8 @@
       <c r="Q117" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R117" s="39" t="s">
-        <v>248</v>
+      <c r="R117" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S117" s="7" t="s">
         <v>22</v>
@@ -9861,8 +9861,8 @@
       <c r="Q118" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R118" s="39" t="s">
-        <v>248</v>
+      <c r="R118" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S118" s="7" t="s">
         <v>22</v>
@@ -9931,8 +9931,8 @@
       <c r="Q119" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R119" s="39" t="s">
-        <v>248</v>
+      <c r="R119" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S119" s="7" t="s">
         <v>22</v>
@@ -10001,8 +10001,8 @@
       <c r="Q120" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R120" s="39" t="s">
-        <v>248</v>
+      <c r="R120" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S120" s="7" t="s">
         <v>22</v>
@@ -10071,8 +10071,8 @@
       <c r="Q121" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R121" s="39" t="s">
-        <v>248</v>
+      <c r="R121" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S121" s="7" t="s">
         <v>22</v>
@@ -10141,8 +10141,8 @@
       <c r="Q122" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R122" s="39" t="s">
-        <v>248</v>
+      <c r="R122" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S122" s="7" t="s">
         <v>22</v>
@@ -10211,8 +10211,8 @@
       <c r="Q123" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R123" s="39" t="s">
-        <v>248</v>
+      <c r="R123" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S123" s="7" t="s">
         <v>22</v>
@@ -10281,8 +10281,8 @@
       <c r="Q124" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R124" s="39" t="s">
-        <v>248</v>
+      <c r="R124" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S124" s="7" t="s">
         <v>22</v>
@@ -10351,8 +10351,8 @@
       <c r="Q125" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R125" s="39" t="s">
-        <v>248</v>
+      <c r="R125" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S125" s="7" t="s">
         <v>22</v>
@@ -10421,8 +10421,8 @@
       <c r="Q126" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R126" s="39" t="s">
-        <v>248</v>
+      <c r="R126" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S126" s="7" t="s">
         <v>22</v>
@@ -10491,8 +10491,8 @@
       <c r="Q127" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R127" s="39" t="s">
-        <v>248</v>
+      <c r="R127" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S127" s="7" t="s">
         <v>22</v>
@@ -10561,8 +10561,8 @@
       <c r="Q128" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R128" s="39" t="s">
-        <v>248</v>
+      <c r="R128" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S128" s="7" t="s">
         <v>22</v>
@@ -10631,8 +10631,8 @@
       <c r="Q129" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R129" s="39" t="s">
-        <v>248</v>
+      <c r="R129" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S129" s="7" t="s">
         <v>22</v>
@@ -10701,8 +10701,8 @@
       <c r="Q130" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R130" s="39" t="s">
-        <v>248</v>
+      <c r="R130" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S130" s="7" t="s">
         <v>22</v>
@@ -10771,8 +10771,8 @@
       <c r="Q131" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R131" s="39" t="s">
-        <v>248</v>
+      <c r="R131" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S131" s="7" t="s">
         <v>22</v>
@@ -10841,8 +10841,8 @@
       <c r="Q132" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R132" s="39" t="s">
-        <v>248</v>
+      <c r="R132" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S132" s="7" t="s">
         <v>22</v>
@@ -10911,8 +10911,8 @@
       <c r="Q133" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R133" s="39" t="s">
-        <v>248</v>
+      <c r="R133" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S133" s="7" t="s">
         <v>22</v>
@@ -10981,8 +10981,8 @@
       <c r="Q134" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R134" s="39" t="s">
-        <v>248</v>
+      <c r="R134" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S134" s="7" t="s">
         <v>22</v>
@@ -11051,8 +11051,8 @@
       <c r="Q135" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R135" s="39" t="s">
-        <v>248</v>
+      <c r="R135" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S135" s="7" t="s">
         <v>22</v>
@@ -11121,8 +11121,8 @@
       <c r="Q136" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R136" s="39" t="s">
-        <v>248</v>
+      <c r="R136" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S136" s="7" t="s">
         <v>22</v>
@@ -11191,8 +11191,8 @@
       <c r="Q137" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R137" s="39" t="s">
-        <v>248</v>
+      <c r="R137" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S137" s="7" t="s">
         <v>17</v>
@@ -11261,8 +11261,8 @@
       <c r="Q138" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R138" s="39" t="s">
-        <v>248</v>
+      <c r="R138" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S138" s="7" t="s">
         <v>17</v>
@@ -11331,8 +11331,8 @@
       <c r="Q139" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R139" s="39" t="s">
-        <v>248</v>
+      <c r="R139" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S139" s="7" t="s">
         <v>17</v>
@@ -11401,8 +11401,8 @@
       <c r="Q140" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R140" s="39" t="s">
-        <v>248</v>
+      <c r="R140" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S140" s="7" t="s">
         <v>17</v>
@@ -11471,8 +11471,8 @@
       <c r="Q141" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R141" s="39" t="s">
-        <v>248</v>
+      <c r="R141" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S141" s="7" t="s">
         <v>17</v>
@@ -11541,8 +11541,8 @@
       <c r="Q142" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R142" s="39" t="s">
-        <v>248</v>
+      <c r="R142" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S142" s="7" t="s">
         <v>17</v>
@@ -11611,8 +11611,8 @@
       <c r="Q143" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R143" s="39" t="s">
-        <v>248</v>
+      <c r="R143" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S143" s="7" t="s">
         <v>17</v>
@@ -11681,8 +11681,8 @@
       <c r="Q144" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R144" s="39" t="s">
-        <v>248</v>
+      <c r="R144" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S144" s="7" t="s">
         <v>17</v>
@@ -11751,8 +11751,8 @@
       <c r="Q145" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R145" s="39" t="s">
-        <v>248</v>
+      <c r="R145" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S145" s="7" t="s">
         <v>17</v>
@@ -11821,8 +11821,8 @@
       <c r="Q146" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R146" s="39" t="s">
-        <v>248</v>
+      <c r="R146" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S146" s="7" t="s">
         <v>17</v>
@@ -11891,8 +11891,8 @@
       <c r="Q147" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R147" s="39" t="s">
-        <v>248</v>
+      <c r="R147" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S147" s="7" t="s">
         <v>17</v>
@@ -11961,8 +11961,8 @@
       <c r="Q148" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R148" s="39" t="s">
-        <v>248</v>
+      <c r="R148" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S148" s="7" t="s">
         <v>17</v>
@@ -12031,8 +12031,8 @@
       <c r="Q149" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R149" s="39" t="s">
-        <v>248</v>
+      <c r="R149" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S149" s="7" t="s">
         <v>17</v>
@@ -12101,8 +12101,8 @@
       <c r="Q150" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R150" s="39" t="s">
-        <v>248</v>
+      <c r="R150" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S150" s="7" t="s">
         <v>17</v>
@@ -12171,8 +12171,8 @@
       <c r="Q151" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R151" s="39" t="s">
-        <v>248</v>
+      <c r="R151" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S151" s="7" t="s">
         <v>17</v>
@@ -12241,8 +12241,8 @@
       <c r="Q152" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R152" s="39" t="s">
-        <v>248</v>
+      <c r="R152" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S152" s="7" t="s">
         <v>17</v>
@@ -12311,8 +12311,8 @@
       <c r="Q153" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R153" s="39" t="s">
-        <v>248</v>
+      <c r="R153" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S153" s="7" t="s">
         <v>17</v>
@@ -12381,8 +12381,8 @@
       <c r="Q154" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R154" s="39" t="s">
-        <v>248</v>
+      <c r="R154" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S154" s="7" t="s">
         <v>17</v>
@@ -12451,8 +12451,8 @@
       <c r="Q155" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R155" s="39" t="s">
-        <v>248</v>
+      <c r="R155" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S155" s="7" t="s">
         <v>17</v>
@@ -12521,8 +12521,8 @@
       <c r="Q156" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R156" s="39" t="s">
-        <v>248</v>
+      <c r="R156" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S156" s="7" t="s">
         <v>17</v>
@@ -12591,8 +12591,8 @@
       <c r="Q157" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R157" s="39" t="s">
-        <v>248</v>
+      <c r="R157" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S157" s="7" t="s">
         <v>17</v>
@@ -12661,8 +12661,8 @@
       <c r="Q158" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R158" s="39" t="s">
-        <v>248</v>
+      <c r="R158" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S158" s="7" t="s">
         <v>17</v>
@@ -12731,8 +12731,8 @@
       <c r="Q159" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R159" s="39" t="s">
-        <v>248</v>
+      <c r="R159" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S159" s="7" t="s">
         <v>22</v>
@@ -12801,8 +12801,8 @@
       <c r="Q160" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R160" s="39" t="s">
-        <v>248</v>
+      <c r="R160" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S160" s="7" t="s">
         <v>22</v>
@@ -12871,8 +12871,8 @@
       <c r="Q161" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R161" s="39" t="s">
-        <v>248</v>
+      <c r="R161" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S161" s="7" t="s">
         <v>22</v>
@@ -12941,8 +12941,8 @@
       <c r="Q162" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R162" s="39" t="s">
-        <v>248</v>
+      <c r="R162" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S162" s="7" t="s">
         <v>22</v>
@@ -13011,8 +13011,8 @@
       <c r="Q163" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R163" s="39" t="s">
-        <v>248</v>
+      <c r="R163" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S163" s="7" t="s">
         <v>22</v>
@@ -13081,8 +13081,8 @@
       <c r="Q164" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R164" s="39" t="s">
-        <v>248</v>
+      <c r="R164" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S164" s="7" t="s">
         <v>22</v>
@@ -13151,8 +13151,8 @@
       <c r="Q165" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R165" s="39" t="s">
-        <v>248</v>
+      <c r="R165" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S165" s="7" t="s">
         <v>22</v>
@@ -13221,8 +13221,8 @@
       <c r="Q166" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R166" s="39" t="s">
-        <v>248</v>
+      <c r="R166" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S166" s="7" t="s">
         <v>22</v>
@@ -13291,8 +13291,8 @@
       <c r="Q167" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R167" s="39" t="s">
-        <v>248</v>
+      <c r="R167" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S167" s="7" t="s">
         <v>22</v>
@@ -13361,8 +13361,8 @@
       <c r="Q168" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R168" s="39" t="s">
-        <v>248</v>
+      <c r="R168" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S168" s="7" t="s">
         <v>22</v>
@@ -13431,8 +13431,8 @@
       <c r="Q169" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R169" s="39" t="s">
-        <v>248</v>
+      <c r="R169" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S169" s="7" t="s">
         <v>22</v>
@@ -13501,8 +13501,8 @@
       <c r="Q170" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R170" s="39" t="s">
-        <v>248</v>
+      <c r="R170" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S170" s="7" t="s">
         <v>22</v>
@@ -13571,8 +13571,8 @@
       <c r="Q171" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R171" s="39" t="s">
-        <v>248</v>
+      <c r="R171" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S171" s="7" t="s">
         <v>22</v>
@@ -13641,8 +13641,8 @@
       <c r="Q172" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R172" s="39" t="s">
-        <v>248</v>
+      <c r="R172" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S172" s="7" t="s">
         <v>22</v>
@@ -13711,8 +13711,8 @@
       <c r="Q173" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R173" s="39" t="s">
-        <v>248</v>
+      <c r="R173" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S173" s="7" t="s">
         <v>22</v>
@@ -13781,8 +13781,8 @@
       <c r="Q174" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R174" s="39" t="s">
-        <v>248</v>
+      <c r="R174" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S174" s="7" t="s">
         <v>22</v>
@@ -13851,8 +13851,8 @@
       <c r="Q175" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R175" s="39" t="s">
-        <v>248</v>
+      <c r="R175" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S175" s="7" t="s">
         <v>22</v>
@@ -13921,8 +13921,8 @@
       <c r="Q176" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R176" s="39" t="s">
-        <v>248</v>
+      <c r="R176" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S176" s="7" t="s">
         <v>22</v>
@@ -13991,8 +13991,8 @@
       <c r="Q177" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R177" s="39" t="s">
-        <v>248</v>
+      <c r="R177" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S177" s="7" t="s">
         <v>22</v>
@@ -14061,8 +14061,8 @@
       <c r="Q178" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R178" s="39" t="s">
-        <v>248</v>
+      <c r="R178" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S178" s="7" t="s">
         <v>22</v>
@@ -14131,8 +14131,8 @@
       <c r="Q179" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R179" s="39" t="s">
-        <v>248</v>
+      <c r="R179" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="S179" s="7" t="s">
         <v>22</v>
@@ -14201,8 +14201,8 @@
       <c r="Q180" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="R180" s="40" t="s">
-        <v>248</v>
+      <c r="R180" s="22" t="s">
+        <v>232</v>
       </c>
       <c r="S180" s="10" t="s">
         <v>22</v>
@@ -14228,11 +14228,22 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="AF2:AF4"/>
-    <mergeCell ref="AG2:AG4"/>
-    <mergeCell ref="AH2:AH4"/>
-    <mergeCell ref="AI2:AI4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="Q2:Q4"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="AJ2:AJ4"/>
     <mergeCell ref="U2:U4"/>
     <mergeCell ref="V2:V4"/>
@@ -14249,23 +14260,12 @@
     <mergeCell ref="AB2:AB4"/>
     <mergeCell ref="AC2:AC4"/>
     <mergeCell ref="AD2:AD4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AG2:AG4"/>
+    <mergeCell ref="AH2:AH4"/>
+    <mergeCell ref="AI2:AI4"/>
     <mergeCell ref="AE2:AE4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="S2:S4"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14280,82 +14280,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/DATA FILES/VFD DATA.xlsx
+++ b/DATA/DATA FILES/VFD DATA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HHpro\DATA\DATA FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9991C58A-3F19-4FC9-8282-1AAD745FEB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF25E08-C3DE-44DF-910D-CBFE8EEBE39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CF7C304B-F6B4-4B1F-B338-76877CE5AAA5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="251">
   <si>
     <t>Motor Data</t>
   </si>
@@ -787,6 +787,12 @@
   </si>
   <si>
     <t>ABB</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -1232,15 +1238,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1250,13 +1247,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1288,6 +1285,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1659,189 +1665,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="28"/>
-      <c r="N1" s="26" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="25"/>
+      <c r="N1" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="28"/>
-      <c r="T1" s="29" t="s">
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="25"/>
+      <c r="T1" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="31"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="41"/>
     </row>
     <row r="2" spans="1:37" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="34"/>
-      <c r="N2" s="23" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="31"/>
+      <c r="N2" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="Q2" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="R2" s="23" t="s">
+      <c r="R2" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="T2" s="23" t="s">
+      <c r="T2" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="U2" s="23" t="s">
+      <c r="U2" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="V2" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="W2" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="X2" s="23" t="s">
+      <c r="X2" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="Y2" s="23" t="s">
+      <c r="Y2" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="Z2" s="23" t="s">
+      <c r="Z2" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="AA2" s="23" t="s">
+      <c r="AA2" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="AB2" s="23" t="s">
+      <c r="AB2" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="AC2" s="23" t="s">
+      <c r="AC2" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="AD2" s="23" t="s">
+      <c r="AD2" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="AE2" s="23" t="s">
+      <c r="AE2" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="AF2" s="23" t="s">
+      <c r="AF2" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="AG2" s="23" t="s">
+      <c r="AG2" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="AH2" s="23" t="s">
+      <c r="AH2" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="AI2" s="23" t="s">
+      <c r="AI2" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="AJ2" s="23" t="s">
+      <c r="AJ2" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="AK2" s="23" t="s">
+      <c r="AK2" s="26" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="38" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="24"/>
-      <c r="AH3" s="24"/>
-      <c r="AI3" s="24"/>
-      <c r="AJ3" s="24"/>
-      <c r="AK3" s="24"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
     </row>
     <row r="4" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
@@ -1853,38 +1859,38 @@
       <c r="C4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="24"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24"/>
-      <c r="AG4" s="24"/>
-      <c r="AH4" s="24"/>
-      <c r="AI4" s="24"/>
-      <c r="AJ4" s="24"/>
-      <c r="AK4" s="24"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -1936,7 +1942,7 @@
         <v>15</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T5" s="17"/>
       <c r="U5" s="18"/>
@@ -2007,7 +2013,7 @@
         <v>15</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T6" s="12"/>
       <c r="U6" s="1"/>
@@ -2078,7 +2084,7 @@
         <v>15</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T7" s="12"/>
       <c r="U7" s="1"/>
@@ -2149,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T8" s="12"/>
       <c r="U8" s="1"/>
@@ -2220,7 +2226,7 @@
         <v>15</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T9" s="12"/>
       <c r="U9" s="1"/>
@@ -2291,7 +2297,7 @@
         <v>15</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T10" s="12"/>
       <c r="U10" s="1"/>
@@ -2362,7 +2368,7 @@
         <v>15</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T11" s="12"/>
       <c r="U11" s="1"/>
@@ -2433,7 +2439,7 @@
         <v>15</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T12" s="12"/>
       <c r="U12" s="1"/>
@@ -2504,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T13" s="12"/>
       <c r="U13" s="1"/>
@@ -2575,7 +2581,7 @@
         <v>15</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T14" s="12"/>
       <c r="U14" s="1"/>
@@ -2646,7 +2652,7 @@
         <v>15</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T15" s="12"/>
       <c r="U15" s="1"/>
@@ -2717,7 +2723,7 @@
         <v>15</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T16" s="12"/>
       <c r="U16" s="1"/>
@@ -2788,7 +2794,7 @@
         <v>15</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T17" s="12"/>
       <c r="U17" s="1"/>
@@ -2859,7 +2865,7 @@
         <v>15</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T18" s="12"/>
       <c r="U18" s="1"/>
@@ -2930,7 +2936,7 @@
         <v>15</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T19" s="12"/>
       <c r="U19" s="1"/>
@@ -3001,7 +3007,7 @@
         <v>15</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T20" s="12"/>
       <c r="U20" s="1"/>
@@ -3072,7 +3078,7 @@
         <v>15</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T21" s="12"/>
       <c r="U21" s="1"/>
@@ -3143,7 +3149,7 @@
         <v>15</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T22" s="12"/>
       <c r="U22" s="1"/>
@@ -3214,7 +3220,7 @@
         <v>15</v>
       </c>
       <c r="R23" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T23" s="12"/>
       <c r="U23" s="1"/>
@@ -3285,7 +3291,7 @@
         <v>15</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T24" s="12"/>
       <c r="U24" s="1"/>
@@ -3356,7 +3362,7 @@
         <v>15</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T25" s="12"/>
       <c r="U25" s="1"/>
@@ -3427,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T26" s="12"/>
       <c r="U26" s="1"/>
@@ -3498,7 +3504,7 @@
         <v>15</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T27" s="12"/>
       <c r="U27" s="1"/>
@@ -3569,7 +3575,7 @@
         <v>15</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T28" s="12"/>
       <c r="U28" s="1"/>
@@ -3640,7 +3646,7 @@
         <v>15</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T29" s="12"/>
       <c r="U29" s="1"/>
@@ -3711,7 +3717,7 @@
         <v>15</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T30" s="12"/>
       <c r="U30" s="1"/>
@@ -3782,7 +3788,7 @@
         <v>15</v>
       </c>
       <c r="R31" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T31" s="12"/>
       <c r="U31" s="1"/>
@@ -3853,7 +3859,7 @@
         <v>15</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T32" s="12"/>
       <c r="U32" s="1"/>
@@ -3924,7 +3930,7 @@
         <v>15</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T33" s="12"/>
       <c r="U33" s="1"/>
@@ -3995,7 +4001,7 @@
         <v>15</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T34" s="12"/>
       <c r="U34" s="1"/>
@@ -4066,7 +4072,7 @@
         <v>15</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T35" s="12"/>
       <c r="U35" s="1"/>
@@ -4137,7 +4143,7 @@
         <v>15</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T36" s="12"/>
       <c r="U36" s="1"/>
@@ -4208,7 +4214,7 @@
         <v>15</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T37" s="12"/>
       <c r="U37" s="1"/>
@@ -4279,7 +4285,7 @@
         <v>15</v>
       </c>
       <c r="R38" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T38" s="12"/>
       <c r="U38" s="1"/>
@@ -4350,7 +4356,7 @@
         <v>15</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T39" s="12"/>
       <c r="U39" s="1"/>
@@ -4421,7 +4427,7 @@
         <v>15</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T40" s="12"/>
       <c r="U40" s="1"/>
@@ -4492,7 +4498,7 @@
         <v>15</v>
       </c>
       <c r="R41" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T41" s="12"/>
       <c r="U41" s="1"/>
@@ -4563,7 +4569,7 @@
         <v>15</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T42" s="12"/>
       <c r="U42" s="1"/>
@@ -4634,7 +4640,7 @@
         <v>15</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T43" s="12"/>
       <c r="U43" s="1"/>
@@ -4705,7 +4711,7 @@
         <v>15</v>
       </c>
       <c r="R44" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T44" s="12"/>
       <c r="U44" s="1"/>
@@ -4776,7 +4782,7 @@
         <v>15</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T45" s="12"/>
       <c r="U45" s="1"/>
@@ -4847,7 +4853,7 @@
         <v>15</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T46" s="12"/>
       <c r="U46" s="1"/>
@@ -4918,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="R47" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T47" s="12"/>
       <c r="U47" s="1"/>
@@ -4989,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="R48" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T48" s="12"/>
       <c r="U48" s="1"/>
@@ -5060,7 +5066,7 @@
         <v>15</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T49" s="12"/>
       <c r="U49" s="1"/>
@@ -5131,7 +5137,7 @@
         <v>15</v>
       </c>
       <c r="R50" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T50" s="12"/>
       <c r="U50" s="1"/>
@@ -5202,7 +5208,7 @@
         <v>15</v>
       </c>
       <c r="R51" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T51" s="12"/>
       <c r="U51" s="1"/>
@@ -5273,7 +5279,7 @@
         <v>15</v>
       </c>
       <c r="R52" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T52" s="12"/>
       <c r="U52" s="1"/>
@@ -5344,7 +5350,7 @@
         <v>15</v>
       </c>
       <c r="R53" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T53" s="12"/>
       <c r="U53" s="1"/>
@@ -5415,7 +5421,7 @@
         <v>15</v>
       </c>
       <c r="R54" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T54" s="12"/>
       <c r="U54" s="1"/>
@@ -5486,7 +5492,7 @@
         <v>15</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T55" s="12"/>
       <c r="U55" s="1"/>
@@ -5557,7 +5563,7 @@
         <v>15</v>
       </c>
       <c r="R56" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T56" s="12"/>
       <c r="U56" s="1"/>
@@ -5628,7 +5634,7 @@
         <v>15</v>
       </c>
       <c r="R57" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T57" s="12"/>
       <c r="U57" s="1"/>
@@ -5699,7 +5705,7 @@
         <v>15</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T58" s="12"/>
       <c r="U58" s="1"/>
@@ -5770,7 +5776,7 @@
         <v>15</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T59" s="12"/>
       <c r="U59" s="1"/>
@@ -5841,7 +5847,7 @@
         <v>15</v>
       </c>
       <c r="R60" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T60" s="12"/>
       <c r="U60" s="1"/>
@@ -5912,7 +5918,7 @@
         <v>15</v>
       </c>
       <c r="R61" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T61" s="12"/>
       <c r="U61" s="1"/>
@@ -5983,7 +5989,7 @@
         <v>15</v>
       </c>
       <c r="R62" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T62" s="12"/>
       <c r="U62" s="1"/>
@@ -6054,7 +6060,7 @@
         <v>15</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T63" s="12"/>
       <c r="U63" s="1"/>
@@ -6125,7 +6131,7 @@
         <v>15</v>
       </c>
       <c r="R64" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T64" s="12"/>
       <c r="U64" s="1"/>
@@ -6196,7 +6202,7 @@
         <v>15</v>
       </c>
       <c r="R65" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T65" s="12"/>
       <c r="U65" s="1"/>
@@ -6267,7 +6273,7 @@
         <v>15</v>
       </c>
       <c r="R66" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T66" s="12"/>
       <c r="U66" s="1"/>
@@ -6338,7 +6344,7 @@
         <v>15</v>
       </c>
       <c r="R67" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T67" s="12"/>
       <c r="U67" s="1"/>
@@ -6409,7 +6415,7 @@
         <v>15</v>
       </c>
       <c r="R68" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T68" s="12"/>
       <c r="U68" s="1"/>
@@ -6480,7 +6486,7 @@
         <v>15</v>
       </c>
       <c r="R69" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T69" s="12"/>
       <c r="U69" s="1"/>
@@ -6551,7 +6557,7 @@
         <v>15</v>
       </c>
       <c r="R70" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T70" s="12"/>
       <c r="U70" s="1"/>
@@ -6622,7 +6628,7 @@
         <v>15</v>
       </c>
       <c r="R71" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T71" s="12"/>
       <c r="U71" s="1"/>
@@ -6693,7 +6699,7 @@
         <v>15</v>
       </c>
       <c r="R72" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T72" s="12"/>
       <c r="U72" s="1"/>
@@ -6764,7 +6770,7 @@
         <v>15</v>
       </c>
       <c r="R73" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T73" s="12"/>
       <c r="U73" s="1"/>
@@ -6835,7 +6841,7 @@
         <v>15</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T74" s="12"/>
       <c r="U74" s="1"/>
@@ -6906,7 +6912,7 @@
         <v>15</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T75" s="12"/>
       <c r="U75" s="1"/>
@@ -6977,7 +6983,7 @@
         <v>15</v>
       </c>
       <c r="R76" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T76" s="12"/>
       <c r="U76" s="1"/>
@@ -7048,7 +7054,7 @@
         <v>15</v>
       </c>
       <c r="R77" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T77" s="12"/>
       <c r="U77" s="1"/>
@@ -7119,7 +7125,7 @@
         <v>15</v>
       </c>
       <c r="R78" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T78" s="12"/>
       <c r="U78" s="1"/>
@@ -7190,7 +7196,7 @@
         <v>15</v>
       </c>
       <c r="R79" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T79" s="12"/>
       <c r="U79" s="1"/>
@@ -7261,7 +7267,7 @@
         <v>15</v>
       </c>
       <c r="R80" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T80" s="12"/>
       <c r="U80" s="1"/>
@@ -7332,7 +7338,7 @@
         <v>15</v>
       </c>
       <c r="R81" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T81" s="12"/>
       <c r="U81" s="1"/>
@@ -7403,7 +7409,7 @@
         <v>15</v>
       </c>
       <c r="R82" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T82" s="12"/>
       <c r="U82" s="1"/>
@@ -7474,7 +7480,7 @@
         <v>15</v>
       </c>
       <c r="R83" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T83" s="12"/>
       <c r="U83" s="1"/>
@@ -7545,7 +7551,7 @@
         <v>15</v>
       </c>
       <c r="R84" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T84" s="12"/>
       <c r="U84" s="1"/>
@@ -7616,7 +7622,7 @@
         <v>15</v>
       </c>
       <c r="R85" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T85" s="12"/>
       <c r="U85" s="1"/>
@@ -7687,7 +7693,7 @@
         <v>15</v>
       </c>
       <c r="R86" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T86" s="12"/>
       <c r="U86" s="1"/>
@@ -7758,7 +7764,7 @@
         <v>15</v>
       </c>
       <c r="R87" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T87" s="12"/>
       <c r="U87" s="1"/>
@@ -7829,7 +7835,7 @@
         <v>15</v>
       </c>
       <c r="R88" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T88" s="12"/>
       <c r="U88" s="1"/>
@@ -7900,7 +7906,7 @@
         <v>15</v>
       </c>
       <c r="R89" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T89" s="12"/>
       <c r="U89" s="1"/>
@@ -7971,7 +7977,7 @@
         <v>15</v>
       </c>
       <c r="R90" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T90" s="12"/>
       <c r="U90" s="1"/>
@@ -8042,7 +8048,7 @@
         <v>15</v>
       </c>
       <c r="R91" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T91" s="12"/>
       <c r="U91" s="1"/>
@@ -8113,7 +8119,7 @@
         <v>15</v>
       </c>
       <c r="R92" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T92" s="12"/>
       <c r="U92" s="1"/>
@@ -8184,7 +8190,7 @@
         <v>228</v>
       </c>
       <c r="R93" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T93" s="12"/>
       <c r="U93" s="1"/>
@@ -8255,7 +8261,7 @@
         <v>228</v>
       </c>
       <c r="R94" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T94" s="12"/>
       <c r="U94" s="1"/>
@@ -8326,7 +8332,7 @@
         <v>228</v>
       </c>
       <c r="R95" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T95" s="12"/>
       <c r="U95" s="1"/>
@@ -8397,7 +8403,7 @@
         <v>228</v>
       </c>
       <c r="R96" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T96" s="12"/>
       <c r="U96" s="1"/>
@@ -8468,7 +8474,7 @@
         <v>228</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T97" s="12"/>
       <c r="U97" s="1"/>
@@ -8539,7 +8545,7 @@
         <v>228</v>
       </c>
       <c r="R98" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T98" s="12"/>
       <c r="U98" s="1"/>
@@ -8610,7 +8616,7 @@
         <v>228</v>
       </c>
       <c r="R99" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T99" s="12"/>
       <c r="U99" s="1"/>
@@ -8681,7 +8687,7 @@
         <v>228</v>
       </c>
       <c r="R100" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T100" s="12"/>
       <c r="U100" s="1"/>
@@ -8752,7 +8758,7 @@
         <v>228</v>
       </c>
       <c r="R101" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T101" s="12"/>
       <c r="U101" s="1"/>
@@ -8823,7 +8829,7 @@
         <v>228</v>
       </c>
       <c r="R102" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T102" s="12"/>
       <c r="U102" s="1"/>
@@ -8894,7 +8900,7 @@
         <v>228</v>
       </c>
       <c r="R103" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T103" s="12"/>
       <c r="U103" s="1"/>
@@ -8965,7 +8971,7 @@
         <v>228</v>
       </c>
       <c r="R104" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T104" s="12"/>
       <c r="U104" s="1"/>
@@ -9036,7 +9042,7 @@
         <v>228</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T105" s="12"/>
       <c r="U105" s="1"/>
@@ -9107,7 +9113,7 @@
         <v>228</v>
       </c>
       <c r="R106" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T106" s="12"/>
       <c r="U106" s="1"/>
@@ -9178,7 +9184,7 @@
         <v>228</v>
       </c>
       <c r="R107" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T107" s="12"/>
       <c r="U107" s="1"/>
@@ -9249,7 +9255,7 @@
         <v>228</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T108" s="12"/>
       <c r="U108" s="1"/>
@@ -9320,7 +9326,7 @@
         <v>228</v>
       </c>
       <c r="R109" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T109" s="12"/>
       <c r="U109" s="1"/>
@@ -9391,7 +9397,7 @@
         <v>228</v>
       </c>
       <c r="R110" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T110" s="12"/>
       <c r="U110" s="1"/>
@@ -9462,7 +9468,7 @@
         <v>228</v>
       </c>
       <c r="R111" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T111" s="12"/>
       <c r="U111" s="1"/>
@@ -9533,7 +9539,7 @@
         <v>228</v>
       </c>
       <c r="R112" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T112" s="12"/>
       <c r="U112" s="1"/>
@@ -9604,7 +9610,7 @@
         <v>228</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T113" s="12"/>
       <c r="U113" s="1"/>
@@ -9675,7 +9681,7 @@
         <v>228</v>
       </c>
       <c r="R114" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T114" s="12"/>
       <c r="U114" s="1"/>
@@ -9746,7 +9752,7 @@
         <v>228</v>
       </c>
       <c r="R115" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T115" s="12"/>
       <c r="U115" s="1"/>
@@ -9817,7 +9823,7 @@
         <v>228</v>
       </c>
       <c r="R116" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T116" s="12"/>
       <c r="U116" s="1"/>
@@ -9888,7 +9894,7 @@
         <v>228</v>
       </c>
       <c r="R117" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T117" s="12"/>
       <c r="U117" s="1"/>
@@ -9959,7 +9965,7 @@
         <v>228</v>
       </c>
       <c r="R118" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T118" s="12"/>
       <c r="U118" s="1"/>
@@ -10030,7 +10036,7 @@
         <v>228</v>
       </c>
       <c r="R119" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T119" s="12"/>
       <c r="U119" s="1"/>
@@ -10101,7 +10107,7 @@
         <v>228</v>
       </c>
       <c r="R120" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T120" s="12"/>
       <c r="U120" s="1"/>
@@ -10172,7 +10178,7 @@
         <v>228</v>
       </c>
       <c r="R121" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T121" s="12"/>
       <c r="U121" s="1"/>
@@ -10243,7 +10249,7 @@
         <v>228</v>
       </c>
       <c r="R122" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T122" s="12"/>
       <c r="U122" s="1"/>
@@ -10314,7 +10320,7 @@
         <v>228</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T123" s="12"/>
       <c r="U123" s="1"/>
@@ -10385,7 +10391,7 @@
         <v>228</v>
       </c>
       <c r="R124" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T124" s="12"/>
       <c r="U124" s="1"/>
@@ -10456,7 +10462,7 @@
         <v>228</v>
       </c>
       <c r="R125" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T125" s="12"/>
       <c r="U125" s="1"/>
@@ -10527,7 +10533,7 @@
         <v>228</v>
       </c>
       <c r="R126" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T126" s="12"/>
       <c r="U126" s="1"/>
@@ -10598,7 +10604,7 @@
         <v>228</v>
       </c>
       <c r="R127" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T127" s="12"/>
       <c r="U127" s="1"/>
@@ -10669,7 +10675,7 @@
         <v>228</v>
       </c>
       <c r="R128" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T128" s="12"/>
       <c r="U128" s="1"/>
@@ -10740,7 +10746,7 @@
         <v>228</v>
       </c>
       <c r="R129" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T129" s="12"/>
       <c r="U129" s="1"/>
@@ -10811,7 +10817,7 @@
         <v>228</v>
       </c>
       <c r="R130" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T130" s="12"/>
       <c r="U130" s="1"/>
@@ -10882,7 +10888,7 @@
         <v>228</v>
       </c>
       <c r="R131" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T131" s="12"/>
       <c r="U131" s="1"/>
@@ -10953,7 +10959,7 @@
         <v>228</v>
       </c>
       <c r="R132" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T132" s="12"/>
       <c r="U132" s="1"/>
@@ -11024,7 +11030,7 @@
         <v>228</v>
       </c>
       <c r="R133" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T133" s="12"/>
       <c r="U133" s="1"/>
@@ -11095,7 +11101,7 @@
         <v>228</v>
       </c>
       <c r="R134" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T134" s="12"/>
       <c r="U134" s="1"/>
@@ -11166,7 +11172,7 @@
         <v>228</v>
       </c>
       <c r="R135" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T135" s="12"/>
       <c r="U135" s="1"/>
@@ -11237,7 +11243,7 @@
         <v>228</v>
       </c>
       <c r="R136" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T136" s="12"/>
       <c r="U136" s="1"/>
@@ -11308,7 +11314,7 @@
         <v>228</v>
       </c>
       <c r="R137" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T137" s="12"/>
       <c r="U137" s="1"/>
@@ -11379,7 +11385,7 @@
         <v>228</v>
       </c>
       <c r="R138" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T138" s="12"/>
       <c r="U138" s="1"/>
@@ -11450,7 +11456,7 @@
         <v>228</v>
       </c>
       <c r="R139" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T139" s="12"/>
       <c r="U139" s="1"/>
@@ -11521,7 +11527,7 @@
         <v>228</v>
       </c>
       <c r="R140" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T140" s="12"/>
       <c r="U140" s="1"/>
@@ -11592,7 +11598,7 @@
         <v>228</v>
       </c>
       <c r="R141" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T141" s="12"/>
       <c r="U141" s="1"/>
@@ -11663,7 +11669,7 @@
         <v>228</v>
       </c>
       <c r="R142" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T142" s="12"/>
       <c r="U142" s="1"/>
@@ -11734,7 +11740,7 @@
         <v>228</v>
       </c>
       <c r="R143" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T143" s="12"/>
       <c r="U143" s="1"/>
@@ -11805,7 +11811,7 @@
         <v>228</v>
       </c>
       <c r="R144" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T144" s="12"/>
       <c r="U144" s="1"/>
@@ -11876,7 +11882,7 @@
         <v>228</v>
       </c>
       <c r="R145" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T145" s="12"/>
       <c r="U145" s="1"/>
@@ -11947,7 +11953,7 @@
         <v>228</v>
       </c>
       <c r="R146" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T146" s="12"/>
       <c r="U146" s="1"/>
@@ -12018,7 +12024,7 @@
         <v>228</v>
       </c>
       <c r="R147" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T147" s="12"/>
       <c r="U147" s="1"/>
@@ -12089,7 +12095,7 @@
         <v>228</v>
       </c>
       <c r="R148" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T148" s="12"/>
       <c r="U148" s="1"/>
@@ -12160,7 +12166,7 @@
         <v>228</v>
       </c>
       <c r="R149" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T149" s="12"/>
       <c r="U149" s="1"/>
@@ -12231,7 +12237,7 @@
         <v>228</v>
       </c>
       <c r="R150" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T150" s="12"/>
       <c r="U150" s="1"/>
@@ -12302,7 +12308,7 @@
         <v>228</v>
       </c>
       <c r="R151" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T151" s="12"/>
       <c r="U151" s="1"/>
@@ -12373,7 +12379,7 @@
         <v>228</v>
       </c>
       <c r="R152" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T152" s="12"/>
       <c r="U152" s="1"/>
@@ -12444,7 +12450,7 @@
         <v>228</v>
       </c>
       <c r="R153" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T153" s="12"/>
       <c r="U153" s="1"/>
@@ -12515,7 +12521,7 @@
         <v>228</v>
       </c>
       <c r="R154" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T154" s="12"/>
       <c r="U154" s="1"/>
@@ -12586,7 +12592,7 @@
         <v>228</v>
       </c>
       <c r="R155" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T155" s="12"/>
       <c r="U155" s="1"/>
@@ -12657,7 +12663,7 @@
         <v>228</v>
       </c>
       <c r="R156" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T156" s="12"/>
       <c r="U156" s="1"/>
@@ -12728,7 +12734,7 @@
         <v>228</v>
       </c>
       <c r="R157" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T157" s="12"/>
       <c r="U157" s="1"/>
@@ -12799,7 +12805,7 @@
         <v>228</v>
       </c>
       <c r="R158" s="7" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="T158" s="12"/>
       <c r="U158" s="1"/>
@@ -12870,7 +12876,7 @@
         <v>228</v>
       </c>
       <c r="R159" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T159" s="12"/>
       <c r="U159" s="1"/>
@@ -12941,7 +12947,7 @@
         <v>228</v>
       </c>
       <c r="R160" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T160" s="12"/>
       <c r="U160" s="1"/>
@@ -13012,7 +13018,7 @@
         <v>228</v>
       </c>
       <c r="R161" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T161" s="12"/>
       <c r="U161" s="1"/>
@@ -13083,7 +13089,7 @@
         <v>228</v>
       </c>
       <c r="R162" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T162" s="12"/>
       <c r="U162" s="1"/>
@@ -13154,7 +13160,7 @@
         <v>228</v>
       </c>
       <c r="R163" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T163" s="12"/>
       <c r="U163" s="1"/>
@@ -13225,7 +13231,7 @@
         <v>228</v>
       </c>
       <c r="R164" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T164" s="12"/>
       <c r="U164" s="1"/>
@@ -13296,7 +13302,7 @@
         <v>228</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T165" s="12"/>
       <c r="U165" s="1"/>
@@ -13367,7 +13373,7 @@
         <v>228</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T166" s="12"/>
       <c r="U166" s="1"/>
@@ -13438,7 +13444,7 @@
         <v>228</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T167" s="12"/>
       <c r="U167" s="1"/>
@@ -13509,7 +13515,7 @@
         <v>228</v>
       </c>
       <c r="R168" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T168" s="12"/>
       <c r="U168" s="1"/>
@@ -13580,7 +13586,7 @@
         <v>228</v>
       </c>
       <c r="R169" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T169" s="12"/>
       <c r="U169" s="1"/>
@@ -13651,7 +13657,7 @@
         <v>228</v>
       </c>
       <c r="R170" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T170" s="12"/>
       <c r="U170" s="1"/>
@@ -13722,7 +13728,7 @@
         <v>228</v>
       </c>
       <c r="R171" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T171" s="12"/>
       <c r="U171" s="1"/>
@@ -13793,7 +13799,7 @@
         <v>228</v>
       </c>
       <c r="R172" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T172" s="12"/>
       <c r="U172" s="1"/>
@@ -13864,7 +13870,7 @@
         <v>228</v>
       </c>
       <c r="R173" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T173" s="12"/>
       <c r="U173" s="1"/>
@@ -13935,7 +13941,7 @@
         <v>228</v>
       </c>
       <c r="R174" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T174" s="12"/>
       <c r="U174" s="1"/>
@@ -14006,7 +14012,7 @@
         <v>228</v>
       </c>
       <c r="R175" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T175" s="12"/>
       <c r="U175" s="1"/>
@@ -14077,7 +14083,7 @@
         <v>228</v>
       </c>
       <c r="R176" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T176" s="12"/>
       <c r="U176" s="1"/>
@@ -14148,7 +14154,7 @@
         <v>228</v>
       </c>
       <c r="R177" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T177" s="12"/>
       <c r="U177" s="1"/>
@@ -14219,7 +14225,7 @@
         <v>228</v>
       </c>
       <c r="R178" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T178" s="12"/>
       <c r="U178" s="1"/>
@@ -14290,7 +14296,7 @@
         <v>228</v>
       </c>
       <c r="R179" s="7" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T179" s="12"/>
       <c r="U179" s="1"/>
@@ -14361,7 +14367,7 @@
         <v>228</v>
       </c>
       <c r="R180" s="10" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="T180" s="14"/>
       <c r="U180" s="15"/>
@@ -14384,21 +14390,11 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="P2:P4"/>
-    <mergeCell ref="R2:R4"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AG2:AG4"/>
+    <mergeCell ref="AH2:AH4"/>
+    <mergeCell ref="AD2:AD4"/>
     <mergeCell ref="AI2:AI4"/>
     <mergeCell ref="T2:T4"/>
     <mergeCell ref="U2:U4"/>
@@ -14415,12 +14411,22 @@
     <mergeCell ref="AA2:AA4"/>
     <mergeCell ref="AB2:AB4"/>
     <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="R2:R4"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J3:J4"/>
     <mergeCell ref="Q2:Q4"/>
-    <mergeCell ref="AE2:AE4"/>
-    <mergeCell ref="AF2:AF4"/>
-    <mergeCell ref="AG2:AG4"/>
-    <mergeCell ref="AH2:AH4"/>
-    <mergeCell ref="AD2:AD4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
